--- a/mlb_weather_professional_v4_1_2026_07_19.xlsx
+++ b/mlb_weather_professional_v4_1_2026_07_19.xlsx
@@ -539,7 +539,7 @@
     <t>C</t>
   </si>
   <si>
-    <t>Density 64 | Wind 45 | Temp 50 | Altitude 58 | Confidence 95%</t>
+    <t>Density 64 | Wind 45 | Temp 49 | Altitude 58 | Confidence 96%</t>
   </si>
   <si>
     <t>Density 68 | Wind 62 | Temp 59 | Altitude 61 | Confidence 92%</t>
@@ -551,7 +551,7 @@
     <t>Density 69 | Wind 38 | Temp 60 | Altitude 61 | Confidence 87%</t>
   </si>
   <si>
-    <t>Density 86 | Wind 54 | Temp 70 | Altitude 73 | Confidence 89%</t>
+    <t>Density 86 | Wind 54 | Temp 71 | Altitude 74 | Confidence 87%</t>
   </si>
   <si>
     <t>Density 69 | Wind 29 | Temp 54 | Altitude 62 | Confidence 91%</t>
@@ -560,7 +560,7 @@
     <t>Density 61 | Wind 50 | Temp 72 | Altitude 56 | Confidence 91%</t>
   </si>
   <si>
-    <t>Density 86 | Wind 41 | Temp 71 | Altitude 73 | Confidence 88%</t>
+    <t>Density 86 | Wind 41 | Temp 71 | Altitude 73 | Confidence 89%</t>
   </si>
   <si>
     <t>Density 72 | Wind 37 | Temp 56 | Altitude 64 | Confidence 94%</t>
@@ -569,22 +569,22 @@
     <t>Density 63 | Wind 23 | Temp 52 | Altitude 58 | Confidence 92%</t>
   </si>
   <si>
-    <t>Density 100 | Wind 44 | Temp 76 | Altitude 100 | Confidence 94%</t>
-  </si>
-  <si>
-    <t>Density 75 | Wind 61 | Temp 72 | Altitude 66 | Confidence 89%</t>
-  </si>
-  <si>
-    <t>Density 71 | Wind 67 | Temp 62 | Altitude 62 | Confidence 92%</t>
+    <t>Density 100 | Wind 44 | Temp 76 | Altitude 100 | Confidence 93%</t>
+  </si>
+  <si>
+    <t>Density 75 | Wind 61 | Temp 71 | Altitude 66 | Confidence 89%</t>
+  </si>
+  <si>
+    <t>Density 71 | Wind 67 | Temp 62 | Altitude 62 | Confidence 91%</t>
   </si>
   <si>
     <t>Density 61 | Wind 46 | Temp 49 | Altitude 56 | Confidence 96%</t>
   </si>
   <si>
-    <t>Density 61 | Wind 50 | Temp 79 | Altitude 57 | Confidence 89%</t>
-  </si>
-  <si>
-    <t>Density 65 | Wind 56 | Temp 54 | Altitude 59 | Confidence 92%</t>
+    <t>Density 61 | Wind 50 | Temp 78 | Altitude 57 | Confidence 90%</t>
+  </si>
+  <si>
+    <t>Density 65 | Wind 56 | Temp 54 | Altitude 59 | Confidence 93%</t>
   </si>
   <si>
     <t>🟨 Neutral</t>
@@ -596,21 +596,21 @@
     <t>🟧 Below Average</t>
   </si>
   <si>
+    <t>WORSENING</t>
+  </si>
+  <si>
+    <t>IMPROVING RAPIDLY</t>
+  </si>
+  <si>
+    <t>IMPROVING</t>
+  </si>
+  <si>
     <t>WORSENING RAPIDLY</t>
   </si>
   <si>
-    <t>IMPROVING RAPIDLY</t>
-  </si>
-  <si>
-    <t>IMPROVING</t>
-  </si>
-  <si>
     <t>STEADY</t>
   </si>
   <si>
-    <t>WORSENING</t>
-  </si>
-  <si>
     <t>LOW</t>
   </si>
   <si>
@@ -623,49 +623,49 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-07-19 08:33:30 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:31 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:33 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:34 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:35 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:36 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:38 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:39 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:40 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:41 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:42 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:43 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:44 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:45 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-19 08:33:47 AM PDT</t>
+    <t>2026-07-19 08:34:10 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:11 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:13 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:14 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:15 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:16 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:18 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:19 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:20 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:21 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:22 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:23 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:24 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:25 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-19 08:34:27 AM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -1001,49 +1001,49 @@
     <t>10:20 PM EDT</t>
   </si>
   <si>
-    <t>2026-07-19 15:33:30 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:31 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:33 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:34 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:35 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:36 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:38 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:39 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:40 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:41 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:42 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:43 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:44 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:45 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-19 15:33:47 UTC</t>
+    <t>2026-07-19 15:34:10 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:11 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:13 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:14 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:15 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:16 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:18 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:19 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:20 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:21 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:22 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:23 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:24 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:25 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-19 15:34:27 UTC</t>
   </si>
   <si>
     <t>2026-07-19T08:29:30+00:00</t>
@@ -1827,7 +1827,7 @@
         <v>143</v>
       </c>
       <c r="K2">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="L2">
         <v>52.8</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="X2" t="s">
         <v>169</v>
@@ -1878,7 +1878,7 @@
         <v>0.4</v>
       </c>
       <c r="AC2">
-        <v>95.3</v>
+        <v>95.8</v>
       </c>
       <c r="AD2" t="s">
         <v>188</v>
@@ -1902,19 +1902,19 @@
         <v>1.1</v>
       </c>
       <c r="AK2">
-        <v>1.1783</v>
+        <v>1.1799</v>
       </c>
       <c r="AL2">
-        <v>1172</v>
+        <v>1130</v>
       </c>
       <c r="AM2">
         <v>1004.1</v>
       </c>
       <c r="AN2">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="AO2">
-        <v>72.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AP2">
         <v>49</v>
@@ -1923,7 +1923,7 @@
         <v>191</v>
       </c>
       <c r="AR2">
-        <v>-4.2</v>
+        <v>-1.6</v>
       </c>
       <c r="AS2">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>143</v>
       </c>
       <c r="K3">
-        <v>78.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L3">
         <v>43.2</v>
@@ -2036,7 +2036,7 @@
         <v>3.3</v>
       </c>
       <c r="AC3">
-        <v>92.3</v>
+        <v>91.5</v>
       </c>
       <c r="AD3" t="s">
         <v>189</v>
@@ -2060,19 +2060,19 @@
         <v>1.6</v>
       </c>
       <c r="AK3">
-        <v>1.1645</v>
+        <v>1.1635</v>
       </c>
       <c r="AL3">
-        <v>1583</v>
+        <v>1611</v>
       </c>
       <c r="AM3">
         <v>1007.6</v>
       </c>
       <c r="AN3">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="AO3">
-        <v>80.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="AP3">
         <v>40.8</v>
@@ -2099,13 +2099,13 @@
         <v>196</v>
       </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="AY3" t="s">
         <v>201</v>
       </c>
       <c r="AZ3">
-        <v>424</v>
+        <v>424.7</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2239,7 +2239,7 @@
         <v>193</v>
       </c>
       <c r="AR4">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AS4">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>202</v>
       </c>
       <c r="AZ4">
-        <v>289.9</v>
+        <v>290.6</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2352,7 +2352,7 @@
         <v>0.4</v>
       </c>
       <c r="AC5">
-        <v>86.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AD5" t="s">
         <v>188</v>
@@ -2376,28 +2376,28 @@
         <v>2.4</v>
       </c>
       <c r="AK5">
-        <v>1.1615</v>
+        <v>1.1613</v>
       </c>
       <c r="AL5">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="AM5">
         <v>1009.1</v>
       </c>
       <c r="AN5">
-        <v>58.9</v>
+        <v>59.1</v>
       </c>
       <c r="AO5">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="AP5">
         <v>47.6</v>
       </c>
       <c r="AQ5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AR5">
-        <v>-4.7</v>
+        <v>-5</v>
       </c>
       <c r="AS5">
         <v>0</v>
@@ -2415,13 +2415,13 @@
         <v>199</v>
       </c>
       <c r="AX5">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="AY5" t="s">
         <v>203</v>
       </c>
       <c r="AZ5">
-        <v>320.2</v>
+        <v>320.8</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2459,7 +2459,7 @@
         <v>144</v>
       </c>
       <c r="K6">
-        <v>90.7</v>
+        <v>91</v>
       </c>
       <c r="L6">
         <v>55.6</v>
@@ -2501,7 +2501,7 @@
         <v>176</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -2510,7 +2510,7 @@
         <v>4.1</v>
       </c>
       <c r="AC6">
-        <v>88.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AD6" t="s">
         <v>189</v>
@@ -2534,28 +2534,28 @@
         <v>0.5</v>
       </c>
       <c r="AK6">
-        <v>1.1056</v>
+        <v>1.1048</v>
       </c>
       <c r="AL6">
-        <v>3233</v>
+        <v>3256</v>
       </c>
       <c r="AM6">
         <v>981.3</v>
       </c>
       <c r="AN6">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AO6">
-        <v>91.5</v>
+        <v>91.8</v>
       </c>
       <c r="AP6">
         <v>52.9</v>
       </c>
       <c r="AQ6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AR6">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AS6">
         <v>0</v>
@@ -2573,13 +2573,13 @@
         <v>196</v>
       </c>
       <c r="AX6">
-        <v>15.3</v>
+        <v>17.6</v>
       </c>
       <c r="AY6" t="s">
         <v>204</v>
       </c>
       <c r="AZ6">
-        <v>546.5</v>
+        <v>547.2</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2617,7 +2617,7 @@
         <v>143</v>
       </c>
       <c r="K7">
-        <v>75.7</v>
+        <v>75.5</v>
       </c>
       <c r="L7">
         <v>56.2</v>
@@ -2668,7 +2668,7 @@
         <v>-0.8</v>
       </c>
       <c r="AC7">
-        <v>90.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="AD7" t="s">
         <v>190</v>
@@ -2692,28 +2692,28 @@
         <v>1.1</v>
       </c>
       <c r="AK7">
-        <v>1.1611</v>
+        <v>1.1615</v>
       </c>
       <c r="AL7">
-        <v>1639</v>
+        <v>1627</v>
       </c>
       <c r="AM7">
         <v>998.1</v>
       </c>
       <c r="AN7">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="AO7">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AP7">
         <v>54.4</v>
       </c>
       <c r="AQ7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AR7">
-        <v>-10</v>
+        <v>-9.9</v>
       </c>
       <c r="AS7">
         <v>0</v>
@@ -2731,13 +2731,13 @@
         <v>196</v>
       </c>
       <c r="AX7">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="AY7" t="s">
         <v>205</v>
       </c>
       <c r="AZ7">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="BA7">
         <v>5</v>
@@ -2859,10 +2859,10 @@
         <v>1013.5</v>
       </c>
       <c r="AN8">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AO8">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AP8">
         <v>53.7</v>
@@ -2889,13 +2889,13 @@
         <v>196</v>
       </c>
       <c r="AX8">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="s">
         <v>206</v>
       </c>
       <c r="AZ8">
-        <v>193</v>
+        <v>193.6</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -2933,7 +2933,7 @@
         <v>144</v>
       </c>
       <c r="K9">
-        <v>91.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="L9">
         <v>54.1</v>
@@ -2984,7 +2984,7 @@
         <v>2.6</v>
       </c>
       <c r="AC9">
-        <v>88.5</v>
+        <v>88.8</v>
       </c>
       <c r="AD9" t="s">
         <v>188</v>
@@ -3008,10 +3008,10 @@
         <v>2</v>
       </c>
       <c r="AK9">
-        <v>1.1049</v>
+        <v>1.105</v>
       </c>
       <c r="AL9">
-        <v>3241</v>
+        <v>3238</v>
       </c>
       <c r="AM9">
         <v>981.9</v>
@@ -3026,10 +3026,10 @@
         <v>53.9</v>
       </c>
       <c r="AQ9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AR9">
-        <v>-9.699999999999999</v>
+        <v>-6</v>
       </c>
       <c r="AS9">
         <v>0</v>
@@ -3047,13 +3047,13 @@
         <v>196</v>
       </c>
       <c r="AX9">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="AY9" t="s">
         <v>207</v>
       </c>
       <c r="AZ9">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3091,7 +3091,7 @@
         <v>143</v>
       </c>
       <c r="K10">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="L10">
         <v>51.8</v>
@@ -3142,7 +3142,7 @@
         <v>0.3</v>
       </c>
       <c r="AC10">
-        <v>94.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="AD10" t="s">
         <v>188</v>
@@ -3166,16 +3166,16 @@
         <v>0.4</v>
       </c>
       <c r="AK10">
-        <v>1.1511</v>
+        <v>1.1513</v>
       </c>
       <c r="AL10">
-        <v>1944</v>
+        <v>1939</v>
       </c>
       <c r="AM10">
-        <v>992.3</v>
+        <v>992.2</v>
       </c>
       <c r="AN10">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
       <c r="AO10">
         <v>77.59999999999999</v>
@@ -3184,10 +3184,10 @@
         <v>48.3</v>
       </c>
       <c r="AQ10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AR10">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AS10">
         <v>0</v>
@@ -3205,13 +3205,13 @@
         <v>196</v>
       </c>
       <c r="AX10">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="AY10" t="s">
         <v>208</v>
       </c>
       <c r="AZ10">
-        <v>61.8</v>
+        <v>62.4</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3249,7 +3249,7 @@
         <v>143</v>
       </c>
       <c r="K11">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="L11">
         <v>67.40000000000001</v>
@@ -3300,7 +3300,7 @@
         <v>-2</v>
       </c>
       <c r="AC11">
-        <v>92</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AD11" t="s">
         <v>190</v>
@@ -3324,28 +3324,28 @@
         <v>2.2</v>
       </c>
       <c r="AK11">
-        <v>1.1801</v>
+        <v>1.1804</v>
       </c>
       <c r="AL11">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="AM11">
         <v>1011.1</v>
       </c>
       <c r="AN11">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
       <c r="AO11">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="AP11">
         <v>65.7</v>
       </c>
       <c r="AQ11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AR11">
-        <v>-15.6</v>
+        <v>-12</v>
       </c>
       <c r="AS11">
         <v>0</v>
@@ -3363,13 +3363,13 @@
         <v>196</v>
       </c>
       <c r="AX11">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY11" t="s">
         <v>209</v>
       </c>
       <c r="AZ11">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3407,7 +3407,7 @@
         <v>143</v>
       </c>
       <c r="K12">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="L12">
         <v>17.9</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="W12">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="X12" t="s">
         <v>170</v>
@@ -3455,10 +3455,10 @@
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AC12">
-        <v>93.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AD12" t="s">
         <v>189</v>
@@ -3482,19 +3482,19 @@
         <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>0.9481000000000001</v>
+        <v>0.9478</v>
       </c>
       <c r="AL12">
-        <v>8603</v>
+        <v>8614</v>
       </c>
       <c r="AM12">
-        <v>844.6</v>
+        <v>844.7</v>
       </c>
       <c r="AN12">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="AO12">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AP12">
         <v>16.1</v>
@@ -3503,7 +3503,7 @@
         <v>193</v>
       </c>
       <c r="AR12">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AS12">
         <v>0</v>
@@ -3521,13 +3521,13 @@
         <v>196</v>
       </c>
       <c r="AX12">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" t="s">
         <v>210</v>
       </c>
       <c r="AZ12">
-        <v>527.2</v>
+        <v>527.9</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3565,7 +3565,7 @@
         <v>145</v>
       </c>
       <c r="K13">
-        <v>90.09999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="L13">
         <v>30.8</v>
@@ -3616,7 +3616,7 @@
         <v>4.1</v>
       </c>
       <c r="AC13">
-        <v>88.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="AD13" t="s">
         <v>189</v>
@@ -3640,19 +3640,19 @@
         <v>1.1</v>
       </c>
       <c r="AK13">
-        <v>1.1427</v>
+        <v>1.1431</v>
       </c>
       <c r="AL13">
-        <v>2289</v>
+        <v>2280</v>
       </c>
       <c r="AM13">
         <v>1011</v>
       </c>
       <c r="AN13">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="AO13">
-        <v>92.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AP13">
         <v>26.8</v>
@@ -3661,7 +3661,7 @@
         <v>193</v>
       </c>
       <c r="AR13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AS13">
         <v>0</v>
@@ -3679,13 +3679,13 @@
         <v>196</v>
       </c>
       <c r="AX13">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="AY13" t="s">
         <v>211</v>
       </c>
       <c r="AZ13">
-        <v>392.8</v>
+        <v>393.4</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3723,7 +3723,7 @@
         <v>143</v>
       </c>
       <c r="K14">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="L14">
         <v>55.3</v>
@@ -3774,7 +3774,7 @@
         <v>4.2</v>
       </c>
       <c r="AC14">
-        <v>92.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="AD14" t="s">
         <v>189</v>
@@ -3798,19 +3798,19 @@
         <v>0.4</v>
       </c>
       <c r="AK14">
-        <v>1.1565</v>
+        <v>1.1557</v>
       </c>
       <c r="AL14">
-        <v>1737</v>
+        <v>1757</v>
       </c>
       <c r="AM14">
         <v>1009.8</v>
       </c>
       <c r="AN14">
-        <v>65</v>
+        <v>65.3</v>
       </c>
       <c r="AO14">
-        <v>83.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AP14">
         <v>54.7</v>
@@ -3819,7 +3819,7 @@
         <v>192</v>
       </c>
       <c r="AR14">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="AS14">
         <v>0</v>
@@ -3837,13 +3837,13 @@
         <v>196</v>
       </c>
       <c r="AX14">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="AY14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AZ14">
-        <v>510.2</v>
+        <v>510.8</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -3881,7 +3881,7 @@
         <v>143</v>
       </c>
       <c r="K15">
-        <v>69.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="L15">
         <v>63.2</v>
@@ -3932,7 +3932,7 @@
         <v>0.1</v>
       </c>
       <c r="AC15">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AD15" t="s">
         <v>188</v>
@@ -3956,28 +3956,28 @@
         <v>0.7</v>
       </c>
       <c r="AK15">
-        <v>1.1894</v>
+        <v>1.1896</v>
       </c>
       <c r="AL15">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="AM15">
         <v>1012.3</v>
       </c>
       <c r="AN15">
-        <v>56.9</v>
+        <v>56.8</v>
       </c>
       <c r="AO15">
-        <v>70.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="AP15">
         <v>59.7</v>
       </c>
       <c r="AQ15" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AR15">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AS15">
         <v>0</v>
@@ -3995,13 +3995,13 @@
         <v>196</v>
       </c>
       <c r="AX15">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AY15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AZ15">
-        <v>547</v>
+        <v>547.7</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4090,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="AC16">
-        <v>88.7</v>
+        <v>90.2</v>
       </c>
       <c r="AD16" t="s">
         <v>188</v>
@@ -4120,13 +4120,13 @@
         <v>858</v>
       </c>
       <c r="AM16">
-        <v>972.1</v>
+        <v>972</v>
       </c>
       <c r="AN16">
-        <v>64.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="AO16">
-        <v>99.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AP16">
         <v>32.4</v>
@@ -4135,7 +4135,7 @@
         <v>193</v>
       </c>
       <c r="AR16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AS16">
         <v>0</v>
@@ -4153,13 +4153,13 @@
         <v>196</v>
       </c>
       <c r="AX16">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AY16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AZ16">
-        <v>281.6</v>
+        <v>282.2</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4197,7 +4197,7 @@
         <v>143</v>
       </c>
       <c r="K17">
-        <v>78.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="L17">
         <v>40.9</v>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="W17">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="X17" t="s">
         <v>169</v>
@@ -4242,13 +4242,13 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB17">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC17">
-        <v>92.3</v>
+        <v>93.2</v>
       </c>
       <c r="AD17" t="s">
         <v>188</v>
@@ -4272,19 +4272,19 @@
         <v>0.7</v>
       </c>
       <c r="AK17">
-        <v>1.1765</v>
+        <v>1.1754</v>
       </c>
       <c r="AL17">
-        <v>1233</v>
+        <v>1261</v>
       </c>
       <c r="AM17">
         <v>1009.4</v>
       </c>
       <c r="AN17">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="AO17">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AP17">
         <v>45.2</v>
@@ -4311,13 +4311,13 @@
         <v>196</v>
       </c>
       <c r="AX17">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="AY17" t="s">
         <v>214</v>
       </c>
       <c r="AZ17">
-        <v>424.3</v>
+        <v>425</v>
       </c>
       <c r="BA17">
         <v>5</v>
@@ -4715,7 +4715,7 @@
         <v>4</v>
       </c>
       <c r="M2">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="N2">
         <v>2.03</v>
@@ -4748,13 +4748,13 @@
         <v>0.25</v>
       </c>
       <c r="X2">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="Y2">
         <v>95.09999999999999</v>
       </c>
       <c r="Z2">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="AA2">
         <v>0.7</v>
@@ -4772,13 +4772,13 @@
         <v>143</v>
       </c>
       <c r="AF2">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="AG2">
-        <v>74.3</v>
+        <v>73.8</v>
       </c>
       <c r="AH2">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="AI2">
         <v>52.8</v>
@@ -4856,13 +4856,13 @@
         <v>0.08</v>
       </c>
       <c r="BH2">
-        <v>1.1827</v>
+        <v>1.1832</v>
       </c>
       <c r="BI2" t="s">
         <v>370</v>
       </c>
       <c r="BJ2">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="BK2" t="s">
         <v>137</v>
@@ -4871,7 +4871,7 @@
         <v>139</v>
       </c>
       <c r="BM2">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="BN2">
         <v>4</v>
@@ -4892,16 +4892,16 @@
         <v>51</v>
       </c>
       <c r="BT2">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="BU2">
         <v>52.1</v>
       </c>
       <c r="BV2">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="BW2">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="BX2">
         <v>0.1</v>
@@ -4916,7 +4916,7 @@
         <v>196</v>
       </c>
       <c r="CC2">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="CD2">
         <v>0</v>
@@ -4960,7 +4960,7 @@
         <v>4</v>
       </c>
       <c r="M3">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="N3">
         <v>1.33</v>
@@ -4993,13 +4993,13 @@
         <v>0.25</v>
       </c>
       <c r="X3">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y3">
-        <v>95.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Z3">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="AA3">
         <v>0.7</v>
@@ -5017,19 +5017,19 @@
         <v>143</v>
       </c>
       <c r="AF3">
-        <v>72.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AG3">
-        <v>77.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AH3">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="AI3">
         <v>49</v>
       </c>
       <c r="AJ3">
-        <v>1004.3</v>
+        <v>1004.2</v>
       </c>
       <c r="AK3">
         <v>1014.8</v>
@@ -5101,13 +5101,13 @@
         <v>0.08</v>
       </c>
       <c r="BH3">
-        <v>1.1782</v>
+        <v>1.1797</v>
       </c>
       <c r="BI3" t="s">
         <v>370</v>
       </c>
       <c r="BJ3">
-        <v>1174</v>
+        <v>1133</v>
       </c>
       <c r="BK3" t="s">
         <v>137</v>
@@ -5116,10 +5116,10 @@
         <v>139</v>
       </c>
       <c r="BM3">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="BN3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO3">
         <v>-3.5</v>
@@ -5131,22 +5131,22 @@
         <v>0</v>
       </c>
       <c r="BR3">
-        <v>1.003</v>
+        <v>1.002</v>
       </c>
       <c r="BS3">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="BT3">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="BU3">
         <v>52.6</v>
       </c>
       <c r="BV3">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="BW3">
-        <v>72.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="BX3">
         <v>0.1</v>
@@ -5161,7 +5161,7 @@
         <v>196</v>
       </c>
       <c r="CC3">
-        <v>72.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="CD3">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="N4">
         <v>0.33</v>
@@ -5238,13 +5238,13 @@
         <v>0.25</v>
       </c>
       <c r="X4">
-        <v>8.6</v>
+        <v>6.3</v>
       </c>
       <c r="Y4">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Z4">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="AA4">
         <v>0.7</v>
@@ -5262,13 +5262,13 @@
         <v>143</v>
       </c>
       <c r="AF4">
-        <v>74.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AG4">
-        <v>79.3</v>
+        <v>76.5</v>
       </c>
       <c r="AH4">
-        <v>51.6</v>
+        <v>50.5</v>
       </c>
       <c r="AI4">
         <v>45.4</v>
@@ -5346,13 +5346,13 @@
         <v>0.08</v>
       </c>
       <c r="BH4">
-        <v>1.1736</v>
+        <v>1.1765</v>
       </c>
       <c r="BI4" t="s">
         <v>370</v>
       </c>
       <c r="BJ4">
-        <v>1312</v>
+        <v>1232</v>
       </c>
       <c r="BK4" t="s">
         <v>137</v>
@@ -5361,10 +5361,10 @@
         <v>139</v>
       </c>
       <c r="BM4">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="BN4">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO4">
         <v>-5.8</v>
@@ -5379,19 +5379,19 @@
         <v>0.998</v>
       </c>
       <c r="BS4">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="BT4">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="BU4">
-        <v>52.2</v>
+        <v>52</v>
       </c>
       <c r="BV4">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="BW4">
-        <v>70.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="BX4">
         <v>0.1</v>
@@ -5406,7 +5406,7 @@
         <v>196</v>
       </c>
       <c r="CC4">
-        <v>74.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="CD4">
         <v>0</v>
@@ -5450,7 +5450,7 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>2.02</v>
+        <v>1.39</v>
       </c>
       <c r="N5">
         <v>1.33</v>
@@ -5483,13 +5483,13 @@
         <v>0.25</v>
       </c>
       <c r="X5">
-        <v>12.1</v>
+        <v>9.6</v>
       </c>
       <c r="Y5">
-        <v>94.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="Z5">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="AA5">
         <v>0.7</v>
@@ -5507,13 +5507,13 @@
         <v>143</v>
       </c>
       <c r="AF5">
-        <v>75.5</v>
+        <v>74.3</v>
       </c>
       <c r="AG5">
-        <v>78.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="AH5">
-        <v>50.1</v>
+        <v>49.1</v>
       </c>
       <c r="AI5">
         <v>41.4</v>
@@ -5591,13 +5591,13 @@
         <v>0.08</v>
       </c>
       <c r="BH5">
-        <v>1.1708</v>
+        <v>1.1736</v>
       </c>
       <c r="BI5" t="s">
         <v>370</v>
       </c>
       <c r="BJ5">
-        <v>1406</v>
+        <v>1329</v>
       </c>
       <c r="BK5" t="s">
         <v>137</v>
@@ -5606,10 +5606,10 @@
         <v>139</v>
       </c>
       <c r="BM5">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="BN5">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
         <v>-7.3</v>
@@ -5624,19 +5624,19 @@
         <v>0.995</v>
       </c>
       <c r="BS5">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="BT5">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="BU5">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="BV5">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="BW5">
-        <v>68.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="BX5">
         <v>0.1</v>
@@ -5651,7 +5651,7 @@
         <v>196</v>
       </c>
       <c r="CC5">
-        <v>75.5</v>
+        <v>74.3</v>
       </c>
       <c r="CD5">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>341</v>
       </c>
       <c r="J6">
-        <v>424</v>
+        <v>424.7</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -5698,7 +5698,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>1.32</v>
+        <v>2.34</v>
       </c>
       <c r="N6">
         <v>1.27</v>
@@ -5731,13 +5731,13 @@
         <v>0.5833</v>
       </c>
       <c r="X6">
-        <v>9.1</v>
+        <v>13.2</v>
       </c>
       <c r="Y6">
-        <v>91.7</v>
+        <v>91.2</v>
       </c>
       <c r="Z6">
-        <v>67.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AA6">
         <v>0.92</v>
@@ -5755,13 +5755,13 @@
         <v>143</v>
       </c>
       <c r="AF6">
-        <v>78.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AG6">
-        <v>77.7</v>
+        <v>80.2</v>
       </c>
       <c r="AH6">
-        <v>53.6</v>
+        <v>54.2</v>
       </c>
       <c r="AI6">
         <v>43.2</v>
@@ -5839,13 +5839,13 @@
         <v>0.12</v>
       </c>
       <c r="BH6">
-        <v>1.1671</v>
+        <v>1.1655</v>
       </c>
       <c r="BI6" t="s">
         <v>370</v>
       </c>
       <c r="BJ6">
-        <v>1503</v>
+        <v>1546</v>
       </c>
       <c r="BK6" t="s">
         <v>137</v>
@@ -5854,10 +5854,10 @@
         <v>140</v>
       </c>
       <c r="BM6">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="BN6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO6">
         <v>11.9</v>
@@ -5869,22 +5869,22 @@
         <v>0</v>
       </c>
       <c r="BR6">
-        <v>1.045</v>
+        <v>1.046</v>
       </c>
       <c r="BS6">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="BT6">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BU6">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="BV6">
-        <v>53.3</v>
+        <v>53.5</v>
       </c>
       <c r="BW6">
-        <v>63.3</v>
+        <v>62.5</v>
       </c>
       <c r="BX6">
         <v>0</v>
@@ -5893,7 +5893,7 @@
         <v>196</v>
       </c>
       <c r="BZ6">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="CA6" t="s">
         <v>196</v>
@@ -5902,7 +5902,7 @@
         <v>79</v>
       </c>
       <c r="CC6">
-        <v>77.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="CD6">
         <v>13</v>
@@ -5940,7 +5940,7 @@
         <v>341</v>
       </c>
       <c r="J7">
-        <v>424</v>
+        <v>424.7</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -5949,7 +5949,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="N7">
         <v>1.37</v>
@@ -5982,13 +5982,13 @@
         <v>0.5833</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="Y7">
-        <v>92.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="Z7">
-        <v>67.5</v>
+        <v>67.3</v>
       </c>
       <c r="AA7">
         <v>0.92</v>
@@ -6006,13 +6006,13 @@
         <v>143</v>
       </c>
       <c r="AF7">
-        <v>80.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="AG7">
-        <v>80.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AH7">
-        <v>53.6</v>
+        <v>54</v>
       </c>
       <c r="AI7">
         <v>40.7</v>
@@ -6090,13 +6090,13 @@
         <v>0.12</v>
       </c>
       <c r="BH7">
-        <v>1.1638</v>
+        <v>1.163</v>
       </c>
       <c r="BI7" t="s">
         <v>370</v>
       </c>
       <c r="BJ7">
-        <v>1602</v>
+        <v>1624</v>
       </c>
       <c r="BK7" t="s">
         <v>137</v>
@@ -6105,10 +6105,10 @@
         <v>140</v>
       </c>
       <c r="BM7">
-        <v>68.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="BN7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO7">
         <v>11.5</v>
@@ -6123,19 +6123,19 @@
         <v>1.045</v>
       </c>
       <c r="BS7">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="BT7">
         <v>64.40000000000001</v>
       </c>
       <c r="BU7">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="BV7">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
       <c r="BW7">
-        <v>61.7</v>
+        <v>61.3</v>
       </c>
       <c r="BX7">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>196</v>
       </c>
       <c r="BZ7">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="CA7" t="s">
         <v>196</v>
@@ -6153,7 +6153,7 @@
         <v>80</v>
       </c>
       <c r="CC7">
-        <v>79.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="CD7">
         <v>12</v>
@@ -6191,7 +6191,7 @@
         <v>341</v>
       </c>
       <c r="J8">
-        <v>424</v>
+        <v>424.7</v>
       </c>
       <c r="K8">
         <v>3</v>
@@ -6200,7 +6200,7 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="N8">
         <v>1.53</v>
@@ -6233,13 +6233,13 @@
         <v>0.5833</v>
       </c>
       <c r="X8">
-        <v>12.8</v>
+        <v>14.3</v>
       </c>
       <c r="Y8">
-        <v>92.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Z8">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AA8">
         <v>0.92</v>
@@ -6257,13 +6257,13 @@
         <v>143</v>
       </c>
       <c r="AF8">
-        <v>81.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="AG8">
-        <v>81.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AH8">
-        <v>52.8</v>
+        <v>53.1</v>
       </c>
       <c r="AI8">
         <v>38.1</v>
@@ -6341,13 +6341,13 @@
         <v>0.12</v>
       </c>
       <c r="BH8">
-        <v>1.1619</v>
+        <v>1.1613</v>
       </c>
       <c r="BI8" t="s">
         <v>370</v>
       </c>
       <c r="BJ8">
-        <v>1666</v>
+        <v>1683</v>
       </c>
       <c r="BK8" t="s">
         <v>137</v>
@@ -6359,7 +6359,7 @@
         <v>68.7</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="BO8">
         <v>11.2</v>
@@ -6374,19 +6374,19 @@
         <v>1.045</v>
       </c>
       <c r="BS8">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="BT8">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="BU8">
         <v>61.8</v>
       </c>
       <c r="BV8">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="BW8">
-        <v>60.6</v>
+        <v>60.3</v>
       </c>
       <c r="BX8">
         <v>0</v>
@@ -6395,7 +6395,7 @@
         <v>196</v>
       </c>
       <c r="BZ8">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="CA8" t="s">
         <v>196</v>
@@ -6404,7 +6404,7 @@
         <v>81</v>
       </c>
       <c r="CC8">
-        <v>80.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="CD8">
         <v>12</v>
@@ -6442,7 +6442,7 @@
         <v>341</v>
       </c>
       <c r="J9">
-        <v>424</v>
+        <v>424.7</v>
       </c>
       <c r="K9">
         <v>4</v>
@@ -6451,7 +6451,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="N9">
         <v>1.82</v>
@@ -6484,13 +6484,13 @@
         <v>0.5833</v>
       </c>
       <c r="X9">
-        <v>13.6</v>
+        <v>15</v>
       </c>
       <c r="Y9">
-        <v>92.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="Z9">
-        <v>66.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AA9">
         <v>0.92</v>
@@ -6508,13 +6508,13 @@
         <v>143</v>
       </c>
       <c r="AF9">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="AG9">
-        <v>80.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="AH9">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="AI9">
         <v>36.7</v>
@@ -6592,13 +6592,13 @@
         <v>0.12</v>
       </c>
       <c r="BH9">
-        <v>1.1618</v>
+        <v>1.1612</v>
       </c>
       <c r="BI9" t="s">
         <v>370</v>
       </c>
       <c r="BJ9">
-        <v>1675</v>
+        <v>1692</v>
       </c>
       <c r="BK9" t="s">
         <v>137</v>
@@ -6607,10 +6607,10 @@
         <v>140</v>
       </c>
       <c r="BM9">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="BN9">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="BO9">
         <v>10.1</v>
@@ -6628,16 +6628,16 @@
         <v>70.7</v>
       </c>
       <c r="BT9">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
       <c r="BU9">
         <v>61</v>
       </c>
       <c r="BV9">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="BW9">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="BX9">
         <v>0</v>
@@ -6646,7 +6646,7 @@
         <v>196</v>
       </c>
       <c r="BZ9">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="CA9" t="s">
         <v>196</v>
@@ -6655,7 +6655,7 @@
         <v>81</v>
       </c>
       <c r="CC9">
-        <v>81.3</v>
+        <v>81.8</v>
       </c>
       <c r="CD9">
         <v>10</v>
@@ -6693,7 +6693,7 @@
         <v>342</v>
       </c>
       <c r="J10">
-        <v>289.9</v>
+        <v>290.6</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -6702,7 +6702,7 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="N10">
         <v>1.99</v>
@@ -6944,7 +6944,7 @@
         <v>342</v>
       </c>
       <c r="J11">
-        <v>289.9</v>
+        <v>290.6</v>
       </c>
       <c r="K11">
         <v>3</v>
@@ -6953,7 +6953,7 @@
         <v>5</v>
       </c>
       <c r="M11">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="N11">
         <v>2.11</v>
@@ -6986,7 +6986,7 @@
         <v>0.5833</v>
       </c>
       <c r="X11">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="Y11">
         <v>93.09999999999999</v>
@@ -7013,10 +7013,10 @@
         <v>80</v>
       </c>
       <c r="AG11">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AH11">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="AI11">
         <v>35.4</v>
@@ -7100,7 +7100,7 @@
         <v>370</v>
       </c>
       <c r="BJ11">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="BK11" t="s">
         <v>137</v>
@@ -7157,7 +7157,7 @@
         <v>79</v>
       </c>
       <c r="CC11">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="CD11">
         <v>13</v>
@@ -7195,7 +7195,7 @@
         <v>342</v>
       </c>
       <c r="J12">
-        <v>289.9</v>
+        <v>290.6</v>
       </c>
       <c r="K12">
         <v>4</v>
@@ -7446,7 +7446,7 @@
         <v>342</v>
       </c>
       <c r="J13">
-        <v>289.9</v>
+        <v>290.6</v>
       </c>
       <c r="K13">
         <v>5</v>
@@ -7697,7 +7697,7 @@
         <v>343</v>
       </c>
       <c r="J14">
-        <v>320.2</v>
+        <v>320.8</v>
       </c>
       <c r="K14">
         <v>2</v>
@@ -7766,7 +7766,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AG14">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="AH14">
         <v>60.1</v>
@@ -7853,7 +7853,7 @@
         <v>370</v>
       </c>
       <c r="BJ14">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="BK14" t="s">
         <v>137</v>
@@ -7948,7 +7948,7 @@
         <v>343</v>
       </c>
       <c r="J15">
-        <v>320.2</v>
+        <v>320.8</v>
       </c>
       <c r="K15">
         <v>3</v>
@@ -7993,7 +7993,7 @@
         <v>5.7</v>
       </c>
       <c r="Y15">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Z15">
         <v>46.7</v>
@@ -8017,10 +8017,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="AG15">
-        <v>83.2</v>
+        <v>83.8</v>
       </c>
       <c r="AH15">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="AI15">
         <v>47.6</v>
@@ -8098,13 +8098,13 @@
         <v>0.09</v>
       </c>
       <c r="BH15">
-        <v>1.161</v>
+        <v>1.1609</v>
       </c>
       <c r="BI15" t="s">
         <v>370</v>
       </c>
       <c r="BJ15">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="BK15" t="s">
         <v>137</v>
@@ -8143,7 +8143,7 @@
         <v>50.4</v>
       </c>
       <c r="BW15">
-        <v>61.1</v>
+        <v>61</v>
       </c>
       <c r="BX15">
         <v>0.1</v>
@@ -8152,7 +8152,7 @@
         <v>196</v>
       </c>
       <c r="BZ15">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="CA15" t="s">
         <v>199</v>
@@ -8161,7 +8161,7 @@
         <v>83</v>
       </c>
       <c r="CC15">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="CD15">
         <v>15</v>
@@ -8199,7 +8199,7 @@
         <v>343</v>
       </c>
       <c r="J16">
-        <v>320.2</v>
+        <v>320.8</v>
       </c>
       <c r="K16">
         <v>4</v>
@@ -8208,7 +8208,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="N16">
         <v>0.61</v>
@@ -8241,10 +8241,10 @@
         <v>0.5833</v>
       </c>
       <c r="X16">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="Y16">
-        <v>90.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z16">
         <v>48.8</v>
@@ -8265,13 +8265,13 @@
         <v>143</v>
       </c>
       <c r="AF16">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AG16">
-        <v>81.7</v>
+        <v>82.8</v>
       </c>
       <c r="AH16">
-        <v>57.7</v>
+        <v>57.9</v>
       </c>
       <c r="AI16">
         <v>44.6</v>
@@ -8349,13 +8349,13 @@
         <v>0.09</v>
       </c>
       <c r="BH16">
-        <v>1.1605</v>
+        <v>1.1601</v>
       </c>
       <c r="BI16" t="s">
         <v>370</v>
       </c>
       <c r="BJ16">
-        <v>1676</v>
+        <v>1687</v>
       </c>
       <c r="BK16" t="s">
         <v>137</v>
@@ -8367,7 +8367,7 @@
         <v>48.7</v>
       </c>
       <c r="BN16">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="BO16">
         <v>-8.9</v>
@@ -8391,10 +8391,10 @@
         <v>55.5</v>
       </c>
       <c r="BV16">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="BW16">
-        <v>61.2</v>
+        <v>61.1</v>
       </c>
       <c r="BX16">
         <v>0</v>
@@ -8403,7 +8403,7 @@
         <v>196</v>
       </c>
       <c r="BZ16">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="CA16" t="s">
         <v>196</v>
@@ -8412,7 +8412,7 @@
         <v>83</v>
       </c>
       <c r="CC16">
-        <v>80.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="CD16">
         <v>10</v>
@@ -8450,7 +8450,7 @@
         <v>343</v>
       </c>
       <c r="J17">
-        <v>320.2</v>
+        <v>320.8</v>
       </c>
       <c r="K17">
         <v>5</v>
@@ -8459,7 +8459,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="N17">
         <v>0.87</v>
@@ -8492,13 +8492,13 @@
         <v>0.5833</v>
       </c>
       <c r="X17">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="Y17">
-        <v>89.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z17">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="AA17">
         <v>0.98</v>
@@ -8516,13 +8516,13 @@
         <v>143</v>
       </c>
       <c r="AF17">
-        <v>82.2</v>
+        <v>82.7</v>
       </c>
       <c r="AG17">
-        <v>79.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AH17">
-        <v>56.3</v>
+        <v>56.8</v>
       </c>
       <c r="AI17">
         <v>42.9</v>
@@ -8600,13 +8600,13 @@
         <v>0.09</v>
       </c>
       <c r="BH17">
-        <v>1.1606</v>
+        <v>1.1596</v>
       </c>
       <c r="BI17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="BJ17">
-        <v>1682</v>
+        <v>1711</v>
       </c>
       <c r="BK17" t="s">
         <v>137</v>
@@ -8615,10 +8615,10 @@
         <v>140</v>
       </c>
       <c r="BM17">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="BN17">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="BO17">
         <v>-10.4</v>
@@ -8630,22 +8630,22 @@
         <v>0</v>
       </c>
       <c r="BR17">
-        <v>0.993</v>
+        <v>0.994</v>
       </c>
       <c r="BS17">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="BT17">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="BU17">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="BV17">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="BW17">
-        <v>61.5</v>
+        <v>61.1</v>
       </c>
       <c r="BX17">
         <v>0</v>
@@ -8654,7 +8654,7 @@
         <v>196</v>
       </c>
       <c r="BZ17">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="CA17" t="s">
         <v>196</v>
@@ -8663,7 +8663,7 @@
         <v>83</v>
       </c>
       <c r="CC17">
-        <v>80.5</v>
+        <v>81.2</v>
       </c>
       <c r="CD17">
         <v>10</v>
@@ -8701,7 +8701,7 @@
         <v>344</v>
       </c>
       <c r="J18">
-        <v>546.5</v>
+        <v>547.2</v>
       </c>
       <c r="K18">
         <v>2</v>
@@ -8710,7 +8710,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>0.93</v>
+        <v>1.3</v>
       </c>
       <c r="N18">
         <v>0.92</v>
@@ -8743,13 +8743,13 @@
         <v>0.5833</v>
       </c>
       <c r="X18">
-        <v>8.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="Y18">
-        <v>91.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="Z18">
-        <v>65.2</v>
+        <v>65</v>
       </c>
       <c r="AA18">
         <v>0.9399999999999999</v>
@@ -8767,13 +8767,13 @@
         <v>144</v>
       </c>
       <c r="AF18">
-        <v>90.7</v>
+        <v>91</v>
       </c>
       <c r="AG18">
-        <v>96.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AH18">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="AI18">
         <v>55.6</v>
@@ -8851,13 +8851,13 @@
         <v>0.1</v>
       </c>
       <c r="BH18">
-        <v>1.1073</v>
+        <v>1.1067</v>
       </c>
       <c r="BI18" t="s">
         <v>371</v>
       </c>
       <c r="BJ18">
-        <v>3165</v>
+        <v>3180</v>
       </c>
       <c r="BK18" t="s">
         <v>137</v>
@@ -8887,16 +8887,16 @@
         <v>64.59999999999999</v>
       </c>
       <c r="BT18">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="BU18">
         <v>59.9</v>
       </c>
       <c r="BV18">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="BW18">
-        <v>46.3</v>
+        <v>45.8</v>
       </c>
       <c r="BX18">
         <v>29.3</v>
@@ -8905,7 +8905,7 @@
         <v>197</v>
       </c>
       <c r="BZ18">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="CA18" t="s">
         <v>196</v>
@@ -8914,7 +8914,7 @@
         <v>90</v>
       </c>
       <c r="CC18">
-        <v>90.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="CD18">
         <v>5</v>
@@ -8952,7 +8952,7 @@
         <v>344</v>
       </c>
       <c r="J19">
-        <v>546.5</v>
+        <v>547.2</v>
       </c>
       <c r="K19">
         <v>3</v>
@@ -8961,7 +8961,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="N19">
         <v>0.62</v>
@@ -8994,13 +8994,13 @@
         <v>0.5833</v>
       </c>
       <c r="X19">
-        <v>10.8</v>
+        <v>13.3</v>
       </c>
       <c r="Y19">
-        <v>89.3</v>
+        <v>87.3</v>
       </c>
       <c r="Z19">
-        <v>64.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AA19">
         <v>0.9399999999999999</v>
@@ -9018,13 +9018,13 @@
         <v>145</v>
       </c>
       <c r="AF19">
-        <v>92</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AG19">
-        <v>98.2</v>
+        <v>101.1</v>
       </c>
       <c r="AH19">
-        <v>70.3</v>
+        <v>70.8</v>
       </c>
       <c r="AI19">
         <v>51.5</v>
@@ -9102,13 +9102,13 @@
         <v>0.1</v>
       </c>
       <c r="BH19">
-        <v>1.1047</v>
+        <v>1.1038</v>
       </c>
       <c r="BI19" t="s">
         <v>371</v>
       </c>
       <c r="BJ19">
-        <v>3265</v>
+        <v>3290</v>
       </c>
       <c r="BK19" t="s">
         <v>137</v>
@@ -9120,7 +9120,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="BN19">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="BO19">
         <v>4</v>
@@ -9135,19 +9135,19 @@
         <v>1.039</v>
       </c>
       <c r="BS19">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="BT19">
-        <v>67.7</v>
+        <v>67.8</v>
       </c>
       <c r="BU19">
         <v>59.8</v>
       </c>
       <c r="BV19">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="BW19">
-        <v>46</v>
+        <v>45.2</v>
       </c>
       <c r="BX19">
         <v>30.9</v>
@@ -9156,7 +9156,7 @@
         <v>197</v>
       </c>
       <c r="BZ19">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="CA19" t="s">
         <v>196</v>
@@ -9165,7 +9165,7 @@
         <v>91</v>
       </c>
       <c r="CC19">
-        <v>91.8</v>
+        <v>92.5</v>
       </c>
       <c r="CD19">
         <v>5</v>
@@ -9203,7 +9203,7 @@
         <v>344</v>
       </c>
       <c r="J20">
-        <v>546.5</v>
+        <v>547.2</v>
       </c>
       <c r="K20">
         <v>4</v>
@@ -9212,7 +9212,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>1.46</v>
+        <v>2.08</v>
       </c>
       <c r="N20">
         <v>0.92</v>
@@ -9245,13 +9245,13 @@
         <v>0.5833</v>
       </c>
       <c r="X20">
-        <v>13.9</v>
+        <v>16.4</v>
       </c>
       <c r="Y20">
-        <v>85.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="Z20">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="AA20">
         <v>0.9399999999999999</v>
@@ -9269,13 +9269,13 @@
         <v>145</v>
       </c>
       <c r="AF20">
-        <v>92.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="AG20">
-        <v>98</v>
+        <v>100.2</v>
       </c>
       <c r="AH20">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AI20">
         <v>50.5</v>
@@ -9353,13 +9353,13 @@
         <v>0.1</v>
       </c>
       <c r="BH20">
-        <v>1.1041</v>
+        <v>1.1031</v>
       </c>
       <c r="BI20" t="s">
         <v>371</v>
       </c>
       <c r="BJ20">
-        <v>3297</v>
+        <v>3323</v>
       </c>
       <c r="BK20" t="s">
         <v>137</v>
@@ -9368,10 +9368,10 @@
         <v>140</v>
       </c>
       <c r="BM20">
-        <v>65.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="BN20">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="BO20">
         <v>3.2</v>
@@ -9386,19 +9386,19 @@
         <v>1.037</v>
       </c>
       <c r="BS20">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="BT20">
-        <v>67.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="BU20">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="BV20">
-        <v>55.3</v>
+        <v>55.5</v>
       </c>
       <c r="BW20">
-        <v>46.9</v>
+        <v>46.1</v>
       </c>
       <c r="BX20">
         <v>31.2</v>
@@ -9407,7 +9407,7 @@
         <v>197</v>
       </c>
       <c r="BZ20">
-        <v>14.2</v>
+        <v>15.6</v>
       </c>
       <c r="CA20" t="s">
         <v>196</v>
@@ -9416,7 +9416,7 @@
         <v>90</v>
       </c>
       <c r="CC20">
-        <v>92.8</v>
+        <v>93.5</v>
       </c>
       <c r="CD20">
         <v>5</v>
@@ -9454,7 +9454,7 @@
         <v>344</v>
       </c>
       <c r="J21">
-        <v>546.5</v>
+        <v>547.2</v>
       </c>
       <c r="K21">
         <v>5</v>
@@ -9463,7 +9463,7 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="N21">
         <v>1.32</v>
@@ -9496,13 +9496,13 @@
         <v>0.5833</v>
       </c>
       <c r="X21">
-        <v>16.3</v>
+        <v>20.4</v>
       </c>
       <c r="Y21">
-        <v>84.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z21">
-        <v>62.9</v>
+        <v>62.5</v>
       </c>
       <c r="AA21">
         <v>0.9399999999999999</v>
@@ -9520,19 +9520,19 @@
         <v>145</v>
       </c>
       <c r="AF21">
-        <v>91.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AG21">
-        <v>96.40000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="AH21">
-        <v>68.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="AI21">
         <v>51.4</v>
       </c>
       <c r="AJ21">
-        <v>980</v>
+        <v>980.1</v>
       </c>
       <c r="AK21">
         <v>1012.2</v>
@@ -9604,13 +9604,13 @@
         <v>0.1</v>
       </c>
       <c r="BH21">
-        <v>1.1047</v>
+        <v>1.1031</v>
       </c>
       <c r="BI21" t="s">
         <v>371</v>
       </c>
       <c r="BJ21">
-        <v>3278</v>
+        <v>3320</v>
       </c>
       <c r="BK21" t="s">
         <v>137</v>
@@ -9619,10 +9619,10 @@
         <v>140</v>
       </c>
       <c r="BM21">
-        <v>65.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="BN21">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="BO21">
         <v>3.2</v>
@@ -9637,19 +9637,19 @@
         <v>1.037</v>
       </c>
       <c r="BS21">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="BT21">
-        <v>67.09999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="BU21">
         <v>59.8</v>
       </c>
       <c r="BV21">
-        <v>55.2</v>
+        <v>55.4</v>
       </c>
       <c r="BW21">
-        <v>47.8</v>
+        <v>46.5</v>
       </c>
       <c r="BX21">
         <v>31.7</v>
@@ -9658,7 +9658,7 @@
         <v>197</v>
       </c>
       <c r="BZ21">
-        <v>15.3</v>
+        <v>17.6</v>
       </c>
       <c r="CA21" t="s">
         <v>196</v>
@@ -9667,7 +9667,7 @@
         <v>89</v>
       </c>
       <c r="CC21">
-        <v>92.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="CD21">
         <v>5</v>
@@ -9705,7 +9705,7 @@
         <v>345</v>
       </c>
       <c r="J22">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="K22">
         <v>2.1</v>
@@ -9714,7 +9714,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="N22">
         <v>1.19</v>
@@ -9747,13 +9747,13 @@
         <v>0.6667</v>
       </c>
       <c r="X22">
-        <v>15</v>
+        <v>13.9</v>
       </c>
       <c r="Y22">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="Z22">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="AA22">
         <v>0.92</v>
@@ -9771,13 +9771,13 @@
         <v>143</v>
       </c>
       <c r="AF22">
-        <v>75.7</v>
+        <v>75.5</v>
       </c>
       <c r="AG22">
-        <v>79.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AH22">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
       <c r="AI22">
         <v>56.2</v>
@@ -9855,13 +9855,13 @@
         <v>0.12</v>
       </c>
       <c r="BH22">
-        <v>1.1618</v>
+        <v>1.1623</v>
       </c>
       <c r="BI22" t="s">
         <v>370</v>
       </c>
       <c r="BJ22">
-        <v>1612</v>
+        <v>1600</v>
       </c>
       <c r="BK22" t="s">
         <v>137</v>
@@ -9870,7 +9870,7 @@
         <v>140</v>
       </c>
       <c r="BM22">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="BN22">
         <v>6</v>
@@ -9888,10 +9888,10 @@
         <v>0.964</v>
       </c>
       <c r="BS22">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="BT22">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="BU22">
         <v>47.8</v>
@@ -9900,7 +9900,7 @@
         <v>47.7</v>
       </c>
       <c r="BW22">
-        <v>68.7</v>
+        <v>69</v>
       </c>
       <c r="BX22">
         <v>0.1</v>
@@ -9909,7 +9909,7 @@
         <v>196</v>
       </c>
       <c r="BZ22">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="CA22" t="s">
         <v>196</v>
@@ -9918,7 +9918,7 @@
         <v>76</v>
       </c>
       <c r="CC22">
-        <v>75.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="CD22">
         <v>10</v>
@@ -9956,7 +9956,7 @@
         <v>345</v>
       </c>
       <c r="J23">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="K23">
         <v>3.1</v>
@@ -9965,7 +9965,7 @@
         <v>5</v>
       </c>
       <c r="M23">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N23">
         <v>1.56</v>
@@ -9998,13 +9998,13 @@
         <v>0.6667</v>
       </c>
       <c r="X23">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="Y23">
-        <v>90.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Z23">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="AA23">
         <v>0.92</v>
@@ -10022,13 +10022,13 @@
         <v>143</v>
       </c>
       <c r="AF23">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AG23">
-        <v>78.8</v>
+        <v>78.2</v>
       </c>
       <c r="AH23">
-        <v>57.9</v>
+        <v>57.7</v>
       </c>
       <c r="AI23">
         <v>54.3</v>
@@ -10106,13 +10106,13 @@
         <v>0.12</v>
       </c>
       <c r="BH23">
-        <v>1.1608</v>
+        <v>1.1611</v>
       </c>
       <c r="BI23" t="s">
         <v>370</v>
       </c>
       <c r="BJ23">
-        <v>1648</v>
+        <v>1639</v>
       </c>
       <c r="BK23" t="s">
         <v>137</v>
@@ -10139,7 +10139,7 @@
         <v>0.966</v>
       </c>
       <c r="BS23">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="BT23">
         <v>36.8</v>
@@ -10151,7 +10151,7 @@
         <v>47.9</v>
       </c>
       <c r="BW23">
-        <v>68.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="BX23">
         <v>0</v>
@@ -10160,7 +10160,7 @@
         <v>196</v>
       </c>
       <c r="BZ23">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="CA23" t="s">
         <v>196</v>
@@ -10169,7 +10169,7 @@
         <v>77</v>
       </c>
       <c r="CC23">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="CD23">
         <v>9</v>
@@ -10207,7 +10207,7 @@
         <v>345</v>
       </c>
       <c r="J24">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="K24">
         <v>4.1</v>
@@ -10216,7 +10216,7 @@
         <v>5</v>
       </c>
       <c r="M24">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="N24">
         <v>1.79</v>
@@ -10249,13 +10249,13 @@
         <v>0.6667</v>
       </c>
       <c r="X24">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="Y24">
-        <v>90.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Z24">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="AA24">
         <v>0.92</v>
@@ -10273,13 +10273,13 @@
         <v>143</v>
       </c>
       <c r="AF24">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AG24">
-        <v>78.7</v>
+        <v>77.7</v>
       </c>
       <c r="AH24">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="AI24">
         <v>53.3</v>
@@ -10357,13 +10357,13 @@
         <v>0.12</v>
       </c>
       <c r="BH24">
-        <v>1.1603</v>
+        <v>1.1609</v>
       </c>
       <c r="BI24" t="s">
         <v>370</v>
       </c>
       <c r="BJ24">
-        <v>1662</v>
+        <v>1646</v>
       </c>
       <c r="BK24" t="s">
         <v>137</v>
@@ -10372,7 +10372,7 @@
         <v>140</v>
       </c>
       <c r="BM24">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="BN24">
         <v>6.1</v>
@@ -10390,10 +10390,10 @@
         <v>0.97</v>
       </c>
       <c r="BS24">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="BT24">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="BU24">
         <v>48.5</v>
@@ -10402,7 +10402,7 @@
         <v>48.1</v>
       </c>
       <c r="BW24">
-        <v>68</v>
+        <v>68.3</v>
       </c>
       <c r="BX24">
         <v>0</v>
@@ -10411,7 +10411,7 @@
         <v>196</v>
       </c>
       <c r="BZ24">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="CA24" t="s">
         <v>196</v>
@@ -10420,7 +10420,7 @@
         <v>77</v>
       </c>
       <c r="CC24">
-        <v>75.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="CD24">
         <v>8</v>
@@ -10458,7 +10458,7 @@
         <v>345</v>
       </c>
       <c r="J25">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="K25">
         <v>5.1</v>
@@ -10467,7 +10467,7 @@
         <v>5</v>
       </c>
       <c r="M25">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="N25">
         <v>1.58</v>
@@ -10500,13 +10500,13 @@
         <v>0.6667</v>
       </c>
       <c r="X25">
-        <v>13.9</v>
+        <v>12.9</v>
       </c>
       <c r="Y25">
-        <v>90.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="Z25">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="AA25">
         <v>0.92</v>
@@ -10524,13 +10524,13 @@
         <v>143</v>
       </c>
       <c r="AF25">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AG25">
-        <v>77</v>
+        <v>76.2</v>
       </c>
       <c r="AH25">
-        <v>55.9</v>
+        <v>55.7</v>
       </c>
       <c r="AI25">
         <v>50.1</v>
@@ -10608,13 +10608,13 @@
         <v>0.12</v>
       </c>
       <c r="BH25">
-        <v>1.1605</v>
+        <v>1.161</v>
       </c>
       <c r="BI25" t="s">
         <v>370</v>
       </c>
       <c r="BJ25">
-        <v>1670</v>
+        <v>1658</v>
       </c>
       <c r="BK25" t="s">
         <v>137</v>
@@ -10653,7 +10653,7 @@
         <v>48.3</v>
       </c>
       <c r="BW25">
-        <v>68.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="BX25">
         <v>0</v>
@@ -10662,7 +10662,7 @@
         <v>196</v>
       </c>
       <c r="BZ25">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="CA25" t="s">
         <v>196</v>
@@ -10671,7 +10671,7 @@
         <v>77</v>
       </c>
       <c r="CC25">
-        <v>75.5</v>
+        <v>75.2</v>
       </c>
       <c r="CD25">
         <v>7</v>
@@ -10709,7 +10709,7 @@
         <v>346</v>
       </c>
       <c r="J26">
-        <v>193</v>
+        <v>193.6</v>
       </c>
       <c r="K26">
         <v>2.6</v>
@@ -10718,7 +10718,7 @@
         <v>5</v>
       </c>
       <c r="M26">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="N26">
         <v>0.26</v>
@@ -10751,10 +10751,10 @@
         <v>0.1667</v>
       </c>
       <c r="X26">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y26">
-        <v>91.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="Z26">
         <v>53.4</v>
@@ -10778,7 +10778,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="AG26">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="AH26">
         <v>74.7</v>
@@ -10913,7 +10913,7 @@
         <v>198</v>
       </c>
       <c r="BZ26">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="CA26" t="s">
         <v>196</v>
@@ -10960,7 +10960,7 @@
         <v>346</v>
       </c>
       <c r="J27">
-        <v>193</v>
+        <v>193.6</v>
       </c>
       <c r="K27">
         <v>3.6</v>
@@ -10969,7 +10969,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N27">
         <v>0.63</v>
@@ -11002,10 +11002,10 @@
         <v>0.1667</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y27">
-        <v>90.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Z27">
         <v>53.3</v>
@@ -11026,13 +11026,13 @@
         <v>143</v>
       </c>
       <c r="AF27">
-        <v>93.5</v>
+        <v>93.3</v>
       </c>
       <c r="AG27">
-        <v>107</v>
+        <v>106.4</v>
       </c>
       <c r="AH27">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="AI27">
         <v>53.4</v>
@@ -11164,7 +11164,7 @@
         <v>198</v>
       </c>
       <c r="BZ27">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="CA27" t="s">
         <v>196</v>
@@ -11173,7 +11173,7 @@
         <v>96</v>
       </c>
       <c r="CC27">
-        <v>91.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="CD27">
         <v>5</v>
@@ -11211,7 +11211,7 @@
         <v>346</v>
       </c>
       <c r="J28">
-        <v>193</v>
+        <v>193.6</v>
       </c>
       <c r="K28">
         <v>4.6</v>
@@ -11220,7 +11220,7 @@
         <v>5</v>
       </c>
       <c r="M28">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="N28">
         <v>1.33</v>
@@ -11253,10 +11253,10 @@
         <v>0.1667</v>
       </c>
       <c r="X28">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Y28">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="Z28">
         <v>53.3</v>
@@ -11277,13 +11277,13 @@
         <v>143</v>
       </c>
       <c r="AF28">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AG28">
-        <v>106.8</v>
+        <v>106.3</v>
       </c>
       <c r="AH28">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AI28">
         <v>50.4</v>
@@ -11415,7 +11415,7 @@
         <v>198</v>
       </c>
       <c r="BZ28">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="CA28" t="s">
         <v>196</v>
@@ -11424,7 +11424,7 @@
         <v>97</v>
       </c>
       <c r="CC28">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="CD28">
         <v>5</v>
@@ -11462,7 +11462,7 @@
         <v>346</v>
       </c>
       <c r="J29">
-        <v>193</v>
+        <v>193.6</v>
       </c>
       <c r="K29">
         <v>5.6</v>
@@ -11471,7 +11471,7 @@
         <v>5</v>
       </c>
       <c r="M29">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="N29">
         <v>1.1</v>
@@ -11504,10 +11504,10 @@
         <v>0.1667</v>
       </c>
       <c r="X29">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="Y29">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="Z29">
         <v>53.3</v>
@@ -11528,13 +11528,13 @@
         <v>143</v>
       </c>
       <c r="AF29">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AG29">
-        <v>106.8</v>
+        <v>106.7</v>
       </c>
       <c r="AH29">
-        <v>72.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AI29">
         <v>47</v>
@@ -11666,7 +11666,7 @@
         <v>198</v>
       </c>
       <c r="BZ29">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="CA29" t="s">
         <v>196</v>
@@ -11675,7 +11675,7 @@
         <v>97</v>
       </c>
       <c r="CC29">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="CD29">
         <v>5</v>
@@ -11713,7 +11713,7 @@
         <v>347</v>
       </c>
       <c r="J30">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="K30">
         <v>2.6</v>
@@ -11722,7 +11722,7 @@
         <v>5</v>
       </c>
       <c r="M30">
-        <v>0.76</v>
+        <v>1.21</v>
       </c>
       <c r="N30">
         <v>0.85</v>
@@ -11755,10 +11755,10 @@
         <v>0.1667</v>
       </c>
       <c r="X30">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="Y30">
-        <v>90.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="Z30">
         <v>53</v>
@@ -11779,19 +11779,19 @@
         <v>144</v>
       </c>
       <c r="AF30">
-        <v>91.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AG30">
-        <v>97.7</v>
+        <v>100.8</v>
       </c>
       <c r="AH30">
-        <v>71.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AI30">
         <v>54.1</v>
       </c>
       <c r="AJ30">
-        <v>982.4</v>
+        <v>982.5</v>
       </c>
       <c r="AK30">
         <v>1013.1</v>
@@ -11863,13 +11863,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BH30">
-        <v>1.1064</v>
+        <v>1.1055</v>
       </c>
       <c r="BI30" t="s">
         <v>371</v>
       </c>
       <c r="BJ30">
-        <v>3196</v>
+        <v>3219</v>
       </c>
       <c r="BK30" t="s">
         <v>137</v>
@@ -11878,10 +11878,10 @@
         <v>140</v>
       </c>
       <c r="BM30">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="BN30">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="BO30">
         <v>-8.4</v>
@@ -11896,19 +11896,19 @@
         <v>1.008</v>
       </c>
       <c r="BS30">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="BT30">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="BU30">
         <v>54.7</v>
       </c>
       <c r="BV30">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="BW30">
-        <v>45.4</v>
+        <v>44.6</v>
       </c>
       <c r="BX30">
         <v>28.3</v>
@@ -11917,7 +11917,7 @@
         <v>197</v>
       </c>
       <c r="BZ30">
-        <v>12.3</v>
+        <v>13.6</v>
       </c>
       <c r="CA30" t="s">
         <v>196</v>
@@ -11926,7 +11926,7 @@
         <v>90</v>
       </c>
       <c r="CC30">
-        <v>91.7</v>
+        <v>92.3</v>
       </c>
       <c r="CD30">
         <v>3</v>
@@ -11964,7 +11964,7 @@
         <v>347</v>
       </c>
       <c r="J31">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="K31">
         <v>3.6</v>
@@ -11973,7 +11973,7 @@
         <v>5</v>
       </c>
       <c r="M31">
-        <v>0.83</v>
+        <v>0.29</v>
       </c>
       <c r="N31">
         <v>0.66</v>
@@ -12006,10 +12006,10 @@
         <v>0.1667</v>
       </c>
       <c r="X31">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="Y31">
-        <v>89.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Z31">
         <v>51.7</v>
@@ -12030,19 +12030,19 @@
         <v>367</v>
       </c>
       <c r="AF31">
-        <v>92.2</v>
+        <v>91.8</v>
       </c>
       <c r="AG31">
-        <v>99</v>
+        <v>97.2</v>
       </c>
       <c r="AH31">
-        <v>72.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="AI31">
         <v>53.9</v>
       </c>
       <c r="AJ31">
-        <v>982</v>
+        <v>981.9</v>
       </c>
       <c r="AK31">
         <v>1012.6</v>
@@ -12114,13 +12114,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BH31">
-        <v>1.1043</v>
+        <v>1.1051</v>
       </c>
       <c r="BI31" t="s">
         <v>371</v>
       </c>
       <c r="BJ31">
-        <v>3258</v>
+        <v>3236</v>
       </c>
       <c r="BK31" t="s">
         <v>137</v>
@@ -12129,10 +12129,10 @@
         <v>140</v>
       </c>
       <c r="BM31">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="BN31">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="BO31">
         <v>-10</v>
@@ -12144,22 +12144,22 @@
         <v>0</v>
       </c>
       <c r="BR31">
-        <v>1.005</v>
+        <v>1.004</v>
       </c>
       <c r="BS31">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="BT31">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="BU31">
         <v>54.3</v>
       </c>
       <c r="BV31">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="BW31">
-        <v>44.2</v>
+        <v>45</v>
       </c>
       <c r="BX31">
         <v>34</v>
@@ -12168,7 +12168,7 @@
         <v>197</v>
       </c>
       <c r="BZ31">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="CA31" t="s">
         <v>196</v>
@@ -12177,7 +12177,7 @@
         <v>91</v>
       </c>
       <c r="CC31">
-        <v>92.2</v>
+        <v>91.5</v>
       </c>
       <c r="CD31">
         <v>3</v>
@@ -12215,7 +12215,7 @@
         <v>347</v>
       </c>
       <c r="J32">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="K32">
         <v>4.6</v>
@@ -12224,7 +12224,7 @@
         <v>5</v>
       </c>
       <c r="M32">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
         <v>1.19</v>
@@ -12257,10 +12257,10 @@
         <v>0.1667</v>
       </c>
       <c r="X32">
-        <v>13.8</v>
+        <v>12.1</v>
       </c>
       <c r="Y32">
-        <v>86.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="Z32">
         <v>51.9</v>
@@ -12281,19 +12281,19 @@
         <v>367</v>
       </c>
       <c r="AF32">
-        <v>92.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AG32">
-        <v>99.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AH32">
-        <v>71.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AI32">
         <v>53.6</v>
       </c>
       <c r="AJ32">
-        <v>981.4</v>
+        <v>981.3</v>
       </c>
       <c r="AK32">
         <v>1012</v>
@@ -12365,13 +12365,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BH32">
-        <v>1.1036</v>
+        <v>1.1044</v>
       </c>
       <c r="BI32" t="s">
         <v>371</v>
       </c>
       <c r="BJ32">
-        <v>3280</v>
+        <v>3259</v>
       </c>
       <c r="BK32" t="s">
         <v>137</v>
@@ -12380,7 +12380,7 @@
         <v>140</v>
       </c>
       <c r="BM32">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="BN32">
         <v>11.5</v>
@@ -12401,16 +12401,16 @@
         <v>51.7</v>
       </c>
       <c r="BT32">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="BU32">
         <v>54.8</v>
       </c>
       <c r="BV32">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="BW32">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="BX32">
         <v>34.4</v>
@@ -12419,7 +12419,7 @@
         <v>197</v>
       </c>
       <c r="BZ32">
-        <v>14</v>
+        <v>12.9</v>
       </c>
       <c r="CA32" t="s">
         <v>196</v>
@@ -12428,7 +12428,7 @@
         <v>91</v>
       </c>
       <c r="CC32">
-        <v>92.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="CD32">
         <v>3</v>
@@ -12466,7 +12466,7 @@
         <v>347</v>
       </c>
       <c r="J33">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="K33">
         <v>5.6</v>
@@ -12475,7 +12475,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="N33">
         <v>1.9</v>
@@ -12508,10 +12508,10 @@
         <v>0.1667</v>
       </c>
       <c r="X33">
-        <v>19.2</v>
+        <v>18</v>
       </c>
       <c r="Y33">
-        <v>84.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="Z33">
         <v>56.8</v>
@@ -12532,19 +12532,19 @@
         <v>367</v>
       </c>
       <c r="AF33">
-        <v>92.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AG33">
-        <v>100.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AH33">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="AI33">
         <v>53.5</v>
       </c>
       <c r="AJ33">
-        <v>981</v>
+        <v>980.9</v>
       </c>
       <c r="AK33">
         <v>1011.6</v>
@@ -12616,13 +12616,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BH33">
-        <v>1.1032</v>
+        <v>1.1037</v>
       </c>
       <c r="BI33" t="s">
         <v>371</v>
       </c>
       <c r="BJ33">
-        <v>3292</v>
+        <v>3277</v>
       </c>
       <c r="BK33" t="s">
         <v>137</v>
@@ -12634,7 +12634,7 @@
         <v>58</v>
       </c>
       <c r="BN33">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="BO33">
         <v>-3.9</v>
@@ -12649,19 +12649,19 @@
         <v>1.019</v>
       </c>
       <c r="BS33">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
       <c r="BT33">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="BU33">
         <v>57.4</v>
       </c>
       <c r="BV33">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="BW33">
-        <v>44.2</v>
+        <v>44.8</v>
       </c>
       <c r="BX33">
         <v>34.5</v>
@@ -12670,7 +12670,7 @@
         <v>197</v>
       </c>
       <c r="BZ33">
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
       <c r="CA33" t="s">
         <v>196</v>
@@ -12679,7 +12679,7 @@
         <v>91</v>
       </c>
       <c r="CC33">
-        <v>92.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="CD33">
         <v>3</v>
@@ -12717,7 +12717,7 @@
         <v>348</v>
       </c>
       <c r="J34">
-        <v>61.8</v>
+        <v>62.4</v>
       </c>
       <c r="K34">
         <v>2.6</v>
@@ -12726,7 +12726,7 @@
         <v>5</v>
       </c>
       <c r="M34">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="N34">
         <v>0.98</v>
@@ -12759,10 +12759,10 @@
         <v>0.1667</v>
       </c>
       <c r="X34">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Y34">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="Z34">
         <v>45.6</v>
@@ -12783,13 +12783,13 @@
         <v>143</v>
       </c>
       <c r="AF34">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="AG34">
-        <v>81</v>
+        <v>80.2</v>
       </c>
       <c r="AH34">
-        <v>58.5</v>
+        <v>58.3</v>
       </c>
       <c r="AI34">
         <v>51.8</v>
@@ -12867,13 +12867,13 @@
         <v>0.1</v>
       </c>
       <c r="BH34">
-        <v>1.1517</v>
+        <v>1.1521</v>
       </c>
       <c r="BI34" t="s">
         <v>371</v>
       </c>
       <c r="BJ34">
-        <v>1912</v>
+        <v>1902</v>
       </c>
       <c r="BK34" t="s">
         <v>137</v>
@@ -12885,7 +12885,7 @@
         <v>45.3</v>
       </c>
       <c r="BN34">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="BO34">
         <v>-12.1</v>
@@ -12900,7 +12900,7 @@
         <v>0.989</v>
       </c>
       <c r="BS34">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="BT34">
         <v>43.8</v>
@@ -12912,7 +12912,7 @@
         <v>49.4</v>
       </c>
       <c r="BW34">
-        <v>66.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="BX34">
         <v>0</v>
@@ -12921,7 +12921,7 @@
         <v>196</v>
       </c>
       <c r="BZ34">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="CA34" t="s">
         <v>196</v>
@@ -12930,7 +12930,7 @@
         <v>78</v>
       </c>
       <c r="CC34">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="CD34">
         <v>10</v>
@@ -12968,7 +12968,7 @@
         <v>348</v>
       </c>
       <c r="J35">
-        <v>61.8</v>
+        <v>62.4</v>
       </c>
       <c r="K35">
         <v>3.6</v>
@@ -12977,7 +12977,7 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="N35">
         <v>0.76</v>
@@ -13010,10 +13010,10 @@
         <v>0.1667</v>
       </c>
       <c r="X35">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y35">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Z35">
         <v>44.6</v>
@@ -13037,7 +13037,7 @@
         <v>77.7</v>
       </c>
       <c r="AG35">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="AH35">
         <v>56.3</v>
@@ -13046,7 +13046,7 @@
         <v>47.9</v>
       </c>
       <c r="AJ35">
-        <v>992.4</v>
+        <v>992.3</v>
       </c>
       <c r="AK35">
         <v>1016.6</v>
@@ -13160,7 +13160,7 @@
         <v>52.6</v>
       </c>
       <c r="BV35">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="BW35">
         <v>66.5</v>
@@ -13172,7 +13172,7 @@
         <v>196</v>
       </c>
       <c r="BZ35">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CA35" t="s">
         <v>196</v>
@@ -13219,7 +13219,7 @@
         <v>348</v>
       </c>
       <c r="J36">
-        <v>61.8</v>
+        <v>62.4</v>
       </c>
       <c r="K36">
         <v>4.6</v>
@@ -13228,7 +13228,7 @@
         <v>5</v>
       </c>
       <c r="M36">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="N36">
         <v>0.82</v>
@@ -13261,10 +13261,10 @@
         <v>0.1667</v>
       </c>
       <c r="X36">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y36">
-        <v>94.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="Z36">
         <v>44</v>
@@ -13288,10 +13288,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="AG36">
-        <v>78.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AH36">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="AI36">
         <v>44.9</v>
@@ -13375,7 +13375,7 @@
         <v>371</v>
       </c>
       <c r="BJ36">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="BK36" t="s">
         <v>137</v>
@@ -13423,7 +13423,7 @@
         <v>196</v>
       </c>
       <c r="BZ36">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CA36" t="s">
         <v>196</v>
@@ -13432,7 +13432,7 @@
         <v>78</v>
       </c>
       <c r="CC36">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="CD36">
         <v>10</v>
@@ -13470,7 +13470,7 @@
         <v>348</v>
       </c>
       <c r="J37">
-        <v>61.8</v>
+        <v>62.4</v>
       </c>
       <c r="K37">
         <v>5.6</v>
@@ -13479,7 +13479,7 @@
         <v>5</v>
       </c>
       <c r="M37">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="N37">
         <v>0.97</v>
@@ -13512,10 +13512,10 @@
         <v>0.1667</v>
       </c>
       <c r="X37">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="Y37">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Z37">
         <v>43.8</v>
@@ -13536,13 +13536,13 @@
         <v>143</v>
       </c>
       <c r="AF37">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AG37">
-        <v>77.2</v>
+        <v>76.7</v>
       </c>
       <c r="AH37">
-        <v>53.4</v>
+        <v>53.2</v>
       </c>
       <c r="AI37">
         <v>42.4</v>
@@ -13620,13 +13620,13 @@
         <v>0.1</v>
       </c>
       <c r="BH37">
-        <v>1.1499</v>
+        <v>1.1503</v>
       </c>
       <c r="BI37" t="s">
         <v>371</v>
       </c>
       <c r="BJ37">
-        <v>2003</v>
+        <v>1994</v>
       </c>
       <c r="BK37" t="s">
         <v>137</v>
@@ -13653,7 +13653,7 @@
         <v>0.984</v>
       </c>
       <c r="BS37">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="BT37">
         <v>42.4</v>
@@ -13665,7 +13665,7 @@
         <v>48.8</v>
       </c>
       <c r="BW37">
-        <v>66.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="BX37">
         <v>0</v>
@@ -13674,7 +13674,7 @@
         <v>196</v>
       </c>
       <c r="BZ37">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CA37" t="s">
         <v>196</v>
@@ -13683,7 +13683,7 @@
         <v>78</v>
       </c>
       <c r="CC37">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="CD37">
         <v>10</v>
@@ -13721,7 +13721,7 @@
         <v>349</v>
       </c>
       <c r="J38">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="K38">
         <v>2.8</v>
@@ -13730,7 +13730,7 @@
         <v>5</v>
       </c>
       <c r="M38">
-        <v>0.6899999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="N38">
         <v>2.27</v>
@@ -13763,13 +13763,13 @@
         <v>0.3333</v>
       </c>
       <c r="X38">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y38">
-        <v>92.2</v>
+        <v>91.3</v>
       </c>
       <c r="Z38">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="AA38">
         <v>1.18</v>
@@ -13787,13 +13787,13 @@
         <v>143</v>
       </c>
       <c r="AF38">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AG38">
-        <v>75.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AH38">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="AI38">
         <v>67.40000000000001</v>
@@ -13871,13 +13871,13 @@
         <v>0.28</v>
       </c>
       <c r="BH38">
-        <v>1.1807</v>
+        <v>1.1813</v>
       </c>
       <c r="BI38" t="s">
         <v>370</v>
       </c>
       <c r="BJ38">
-        <v>1029</v>
+        <v>1014</v>
       </c>
       <c r="BK38" t="s">
         <v>137</v>
@@ -13886,7 +13886,7 @@
         <v>140</v>
       </c>
       <c r="BM38">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="BN38">
         <v>4.2</v>
@@ -13904,19 +13904,19 @@
         <v>0.951</v>
       </c>
       <c r="BS38">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="BT38">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="BU38">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="BV38">
         <v>46.9</v>
       </c>
       <c r="BW38">
-        <v>70.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="BX38">
         <v>0</v>
@@ -13925,7 +13925,7 @@
         <v>196</v>
       </c>
       <c r="BZ38">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="CA38" t="s">
         <v>196</v>
@@ -13934,7 +13934,7 @@
         <v>75</v>
       </c>
       <c r="CC38">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="CD38">
         <v>10</v>
@@ -13972,7 +13972,7 @@
         <v>349</v>
       </c>
       <c r="J39">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="K39">
         <v>3.8</v>
@@ -13981,7 +13981,7 @@
         <v>5</v>
       </c>
       <c r="M39">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="N39">
         <v>2.42</v>
@@ -14014,13 +14014,13 @@
         <v>0.3333</v>
       </c>
       <c r="X39">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="Y39">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="Z39">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="AA39">
         <v>1.18</v>
@@ -14038,13 +14038,13 @@
         <v>143</v>
       </c>
       <c r="AF39">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="AG39">
-        <v>74.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="AH39">
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
       <c r="AI39">
         <v>65.90000000000001</v>
@@ -14122,13 +14122,13 @@
         <v>0.28</v>
       </c>
       <c r="BH39">
-        <v>1.1802</v>
+        <v>1.1804</v>
       </c>
       <c r="BI39" t="s">
         <v>370</v>
       </c>
       <c r="BJ39">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="BK39" t="s">
         <v>137</v>
@@ -14137,10 +14137,10 @@
         <v>140</v>
       </c>
       <c r="BM39">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="BN39">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO39">
         <v>-26.4</v>
@@ -14161,13 +14161,13 @@
         <v>32.5</v>
       </c>
       <c r="BU39">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="BV39">
         <v>46.9</v>
       </c>
       <c r="BW39">
-        <v>70</v>
+        <v>70.2</v>
       </c>
       <c r="BX39">
         <v>0</v>
@@ -14176,7 +14176,7 @@
         <v>196</v>
       </c>
       <c r="BZ39">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="CA39" t="s">
         <v>196</v>
@@ -14185,7 +14185,7 @@
         <v>75</v>
       </c>
       <c r="CC39">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="CD39">
         <v>10</v>
@@ -14223,7 +14223,7 @@
         <v>349</v>
       </c>
       <c r="J40">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="K40">
         <v>4.8</v>
@@ -14232,7 +14232,7 @@
         <v>5</v>
       </c>
       <c r="M40">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="N40">
         <v>2.14</v>
@@ -14265,10 +14265,10 @@
         <v>0.3333</v>
       </c>
       <c r="X40">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="Y40">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Z40">
         <v>32.1</v>
@@ -14292,7 +14292,7 @@
         <v>74</v>
       </c>
       <c r="AG40">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="AH40">
         <v>61.2</v>
@@ -14379,7 +14379,7 @@
         <v>370</v>
       </c>
       <c r="BJ40">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="BK40" t="s">
         <v>137</v>
@@ -14427,7 +14427,7 @@
         <v>196</v>
       </c>
       <c r="BZ40">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="CA40" t="s">
         <v>196</v>
@@ -14474,7 +14474,7 @@
         <v>349</v>
       </c>
       <c r="J41">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="K41">
         <v>5.8</v>
@@ -14483,7 +14483,7 @@
         <v>5</v>
       </c>
       <c r="M41">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="N41">
         <v>1.59</v>
@@ -14516,10 +14516,10 @@
         <v>0.3333</v>
       </c>
       <c r="X41">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y41">
-        <v>92</v>
+        <v>92.2</v>
       </c>
       <c r="Z41">
         <v>32.4</v>
@@ -14540,13 +14540,13 @@
         <v>143</v>
       </c>
       <c r="AF41">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="AG41">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AH41">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="AI41">
         <v>62.2</v>
@@ -14630,7 +14630,7 @@
         <v>370</v>
       </c>
       <c r="BJ41">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="BK41" t="s">
         <v>137</v>
@@ -14678,7 +14678,7 @@
         <v>196</v>
       </c>
       <c r="BZ41">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="CA41" t="s">
         <v>196</v>
@@ -14687,7 +14687,7 @@
         <v>75</v>
       </c>
       <c r="CC41">
-        <v>73.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="CD41">
         <v>10</v>
@@ -14725,7 +14725,7 @@
         <v>350</v>
       </c>
       <c r="J42">
-        <v>527.2</v>
+        <v>527.9</v>
       </c>
       <c r="K42">
         <v>3.6</v>
@@ -14734,7 +14734,7 @@
         <v>5</v>
       </c>
       <c r="M42">
-        <v>0.36</v>
+        <v>0.59</v>
       </c>
       <c r="N42">
         <v>1.37</v>
@@ -14767,13 +14767,13 @@
         <v>0.1667</v>
       </c>
       <c r="X42">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y42">
-        <v>94.2</v>
+        <v>93.3</v>
       </c>
       <c r="Z42">
-        <v>70.5</v>
+        <v>70.3</v>
       </c>
       <c r="AA42">
         <v>1.05</v>
@@ -14791,19 +14791,19 @@
         <v>143</v>
       </c>
       <c r="AF42">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AG42">
-        <v>96.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="AH42">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="AI42">
         <v>17.9</v>
       </c>
       <c r="AJ42">
-        <v>845.1</v>
+        <v>845.2</v>
       </c>
       <c r="AK42">
         <v>1006.2</v>
@@ -14875,13 +14875,13 @@
         <v>0.08</v>
       </c>
       <c r="BH42">
-        <v>0.9510999999999999</v>
+        <v>0.9508</v>
       </c>
       <c r="BI42" t="s">
         <v>372</v>
       </c>
       <c r="BJ42">
-        <v>8479</v>
+        <v>8491</v>
       </c>
       <c r="BK42" t="s">
         <v>137</v>
@@ -14920,7 +14920,7 @@
         <v>52.6</v>
       </c>
       <c r="BW42">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
       <c r="BX42">
         <v>0.2</v>
@@ -14929,7 +14929,7 @@
         <v>196</v>
       </c>
       <c r="BZ42">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="CA42" t="s">
         <v>196</v>
@@ -14938,7 +14938,7 @@
         <v>93</v>
       </c>
       <c r="CC42">
-        <v>95.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="CD42">
         <v>5</v>
@@ -14976,7 +14976,7 @@
         <v>350</v>
       </c>
       <c r="J43">
-        <v>527.2</v>
+        <v>527.9</v>
       </c>
       <c r="K43">
         <v>4.6</v>
@@ -14985,7 +14985,7 @@
         <v>5</v>
       </c>
       <c r="M43">
-        <v>0.11</v>
+        <v>0.52</v>
       </c>
       <c r="N43">
         <v>1.54</v>
@@ -15018,13 +15018,13 @@
         <v>0.1667</v>
       </c>
       <c r="X43">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="Y43">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Z43">
-        <v>69.3</v>
+        <v>69</v>
       </c>
       <c r="AA43">
         <v>1.05</v>
@@ -15042,19 +15042,19 @@
         <v>143</v>
       </c>
       <c r="AF43">
-        <v>97.3</v>
+        <v>97.5</v>
       </c>
       <c r="AG43">
-        <v>96.2</v>
+        <v>97.2</v>
       </c>
       <c r="AH43">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="AI43">
         <v>15.7</v>
       </c>
       <c r="AJ43">
-        <v>844.6</v>
+        <v>844.7</v>
       </c>
       <c r="AK43">
         <v>1005.1</v>
@@ -15126,13 +15126,13 @@
         <v>0.08</v>
       </c>
       <c r="BH43">
-        <v>0.9471000000000001</v>
+        <v>0.9467</v>
       </c>
       <c r="BI43" t="s">
         <v>372</v>
       </c>
       <c r="BJ43">
-        <v>8641</v>
+        <v>8655</v>
       </c>
       <c r="BK43" t="s">
         <v>137</v>
@@ -15168,10 +15168,10 @@
         <v>63.9</v>
       </c>
       <c r="BV43">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="BW43">
-        <v>45</v>
+        <v>44.7</v>
       </c>
       <c r="BX43">
         <v>0.6</v>
@@ -15180,7 +15180,7 @@
         <v>196</v>
       </c>
       <c r="BZ43">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="CA43" t="s">
         <v>196</v>
@@ -15189,7 +15189,7 @@
         <v>96</v>
       </c>
       <c r="CC43">
-        <v>97.3</v>
+        <v>97.8</v>
       </c>
       <c r="CD43">
         <v>5</v>
@@ -15227,7 +15227,7 @@
         <v>350</v>
       </c>
       <c r="J44">
-        <v>527.2</v>
+        <v>527.9</v>
       </c>
       <c r="K44">
         <v>5.6</v>
@@ -15236,7 +15236,7 @@
         <v>5</v>
       </c>
       <c r="M44">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="N44">
         <v>1.68</v>
@@ -15269,13 +15269,13 @@
         <v>0.1667</v>
       </c>
       <c r="X44">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y44">
-        <v>93.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="Z44">
-        <v>67.7</v>
+        <v>67.5</v>
       </c>
       <c r="AA44">
         <v>1.05</v>
@@ -15293,19 +15293,19 @@
         <v>143</v>
       </c>
       <c r="AF44">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AG44">
-        <v>95.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AH44">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="AI44">
         <v>14.2</v>
       </c>
       <c r="AJ44">
-        <v>844.1</v>
+        <v>844.2</v>
       </c>
       <c r="AK44">
         <v>1004.3</v>
@@ -15377,13 +15377,13 @@
         <v>0.08</v>
       </c>
       <c r="BH44">
-        <v>0.9452</v>
+        <v>0.9449</v>
       </c>
       <c r="BI44" t="s">
         <v>372</v>
       </c>
       <c r="BJ44">
-        <v>8721</v>
+        <v>8731</v>
       </c>
       <c r="BK44" t="s">
         <v>137</v>
@@ -15422,7 +15422,7 @@
         <v>52.5</v>
       </c>
       <c r="BW44">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="BX44">
         <v>0.6</v>
@@ -15431,7 +15431,7 @@
         <v>196</v>
       </c>
       <c r="BZ44">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="CA44" t="s">
         <v>196</v>
@@ -15440,7 +15440,7 @@
         <v>97</v>
       </c>
       <c r="CC44">
-        <v>98.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="CD44">
         <v>5</v>
@@ -15478,7 +15478,7 @@
         <v>350</v>
       </c>
       <c r="J45">
-        <v>527.2</v>
+        <v>527.9</v>
       </c>
       <c r="K45">
         <v>6.6</v>
@@ -15487,7 +15487,7 @@
         <v>5</v>
       </c>
       <c r="M45">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="N45">
         <v>1.65</v>
@@ -15520,10 +15520,10 @@
         <v>0.1667</v>
       </c>
       <c r="X45">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y45">
-        <v>90.8</v>
+        <v>91</v>
       </c>
       <c r="Z45">
         <v>66.90000000000001</v>
@@ -15544,7 +15544,7 @@
         <v>143</v>
       </c>
       <c r="AF45">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AG45">
         <v>95.2</v>
@@ -15556,7 +15556,7 @@
         <v>14.1</v>
       </c>
       <c r="AJ45">
-        <v>844</v>
+        <v>843.9</v>
       </c>
       <c r="AK45">
         <v>1003.9</v>
@@ -15628,13 +15628,13 @@
         <v>0.08</v>
       </c>
       <c r="BH45">
-        <v>0.9444</v>
+        <v>0.9445</v>
       </c>
       <c r="BI45" t="s">
         <v>372</v>
       </c>
       <c r="BJ45">
-        <v>8751</v>
+        <v>8749</v>
       </c>
       <c r="BK45" t="s">
         <v>137</v>
@@ -15682,7 +15682,7 @@
         <v>196</v>
       </c>
       <c r="BZ45">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CA45" t="s">
         <v>196</v>
@@ -15691,7 +15691,7 @@
         <v>97</v>
       </c>
       <c r="CC45">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="CD45">
         <v>5</v>
@@ -15729,7 +15729,7 @@
         <v>351</v>
       </c>
       <c r="J46">
-        <v>392.8</v>
+        <v>393.4</v>
       </c>
       <c r="K46">
         <v>4.5</v>
@@ -15738,7 +15738,7 @@
         <v>5</v>
       </c>
       <c r="M46">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="N46">
         <v>1.67</v>
@@ -15771,13 +15771,13 @@
         <v>0.0833</v>
       </c>
       <c r="X46">
-        <v>15.1</v>
+        <v>13.4</v>
       </c>
       <c r="Y46">
-        <v>87.2</v>
+        <v>88.5</v>
       </c>
       <c r="Z46">
-        <v>65.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="AA46">
         <v>1.08</v>
@@ -15795,13 +15795,13 @@
         <v>145</v>
       </c>
       <c r="AF46">
-        <v>90.09999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="AG46">
-        <v>94.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="AH46">
-        <v>52.6</v>
+        <v>52.3</v>
       </c>
       <c r="AI46">
         <v>30.8</v>
@@ -15879,13 +15879,13 @@
         <v>0.1</v>
       </c>
       <c r="BH46">
-        <v>1.148</v>
+        <v>1.1487</v>
       </c>
       <c r="BI46" t="s">
         <v>371</v>
       </c>
       <c r="BJ46">
-        <v>2107</v>
+        <v>2089</v>
       </c>
       <c r="BK46" t="s">
         <v>137</v>
@@ -15894,10 +15894,10 @@
         <v>140</v>
       </c>
       <c r="BM46">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="BN46">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="BO46">
         <v>8.6</v>
@@ -15915,7 +15915,7 @@
         <v>67.90000000000001</v>
       </c>
       <c r="BT46">
-        <v>66</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="BU46">
         <v>57.9</v>
@@ -15924,7 +15924,7 @@
         <v>54.6</v>
       </c>
       <c r="BW46">
-        <v>52.9</v>
+        <v>53.2</v>
       </c>
       <c r="BX46">
         <v>0.2</v>
@@ -15933,7 +15933,7 @@
         <v>196</v>
       </c>
       <c r="BZ46">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CA46" t="s">
         <v>196</v>
@@ -15942,7 +15942,7 @@
         <v>86</v>
       </c>
       <c r="CC46">
-        <v>89.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="CD46">
         <v>3</v>
@@ -15980,7 +15980,7 @@
         <v>351</v>
       </c>
       <c r="J47">
-        <v>392.8</v>
+        <v>393.4</v>
       </c>
       <c r="K47">
         <v>5.5</v>
@@ -15989,7 +15989,7 @@
         <v>5</v>
       </c>
       <c r="M47">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -16022,13 +16022,13 @@
         <v>0.0833</v>
       </c>
       <c r="X47">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="Y47">
-        <v>88.2</v>
+        <v>88.8</v>
       </c>
       <c r="Z47">
-        <v>66.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AA47">
         <v>1.08</v>
@@ -16046,13 +16046,13 @@
         <v>144</v>
       </c>
       <c r="AF47">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="AG47">
-        <v>96.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AH47">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="AI47">
         <v>26.3</v>
@@ -16130,13 +16130,13 @@
         <v>0.1</v>
       </c>
       <c r="BH47">
-        <v>1.1414</v>
+        <v>1.1417</v>
       </c>
       <c r="BI47" t="s">
         <v>371</v>
       </c>
       <c r="BJ47">
-        <v>2329</v>
+        <v>2320</v>
       </c>
       <c r="BK47" t="s">
         <v>137</v>
@@ -16145,7 +16145,7 @@
         <v>140</v>
       </c>
       <c r="BM47">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="BN47">
         <v>7.9</v>
@@ -16166,7 +16166,7 @@
         <v>69</v>
       </c>
       <c r="BT47">
-        <v>68.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="BU47">
         <v>58</v>
@@ -16175,7 +16175,7 @@
         <v>55.2</v>
       </c>
       <c r="BW47">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="BX47">
         <v>0.1</v>
@@ -16184,7 +16184,7 @@
         <v>196</v>
       </c>
       <c r="BZ47">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="CA47" t="s">
         <v>196</v>
@@ -16193,7 +16193,7 @@
         <v>89</v>
       </c>
       <c r="CC47">
-        <v>92.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="CD47">
         <v>3</v>
@@ -16231,7 +16231,7 @@
         <v>351</v>
       </c>
       <c r="J48">
-        <v>392.8</v>
+        <v>393.4</v>
       </c>
       <c r="K48">
         <v>6.5</v>
@@ -16240,7 +16240,7 @@
         <v>5</v>
       </c>
       <c r="M48">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="N48">
         <v>1.34</v>
@@ -16273,13 +16273,13 @@
         <v>0.0833</v>
       </c>
       <c r="X48">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="Y48">
-        <v>90.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="Z48">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AA48">
         <v>1.08</v>
@@ -16297,13 +16297,13 @@
         <v>144</v>
       </c>
       <c r="AF48">
-        <v>94.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="AG48">
-        <v>94.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AH48">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="AI48">
         <v>22.9</v>
@@ -16381,13 +16381,13 @@
         <v>0.1</v>
       </c>
       <c r="BH48">
-        <v>1.1376</v>
+        <v>1.1373</v>
       </c>
       <c r="BI48" t="s">
         <v>371</v>
       </c>
       <c r="BJ48">
-        <v>2465</v>
+        <v>2473</v>
       </c>
       <c r="BK48" t="s">
         <v>137</v>
@@ -16396,7 +16396,7 @@
         <v>140</v>
       </c>
       <c r="BM48">
-        <v>72.7</v>
+        <v>72.8</v>
       </c>
       <c r="BN48">
         <v>8.300000000000001</v>
@@ -16417,16 +16417,16 @@
         <v>72</v>
       </c>
       <c r="BT48">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="BU48">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="BV48">
         <v>56</v>
       </c>
       <c r="BW48">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
       <c r="BX48">
         <v>0.1</v>
@@ -16435,7 +16435,7 @@
         <v>196</v>
       </c>
       <c r="BZ48">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="CA48" t="s">
         <v>196</v>
@@ -16444,7 +16444,7 @@
         <v>91</v>
       </c>
       <c r="CC48">
-        <v>94.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="CD48">
         <v>5</v>
@@ -16482,7 +16482,7 @@
         <v>351</v>
       </c>
       <c r="J49">
-        <v>392.8</v>
+        <v>393.4</v>
       </c>
       <c r="K49">
         <v>7.5</v>
@@ -16491,7 +16491,7 @@
         <v>5</v>
       </c>
       <c r="M49">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="N49">
         <v>1.78</v>
@@ -16524,10 +16524,10 @@
         <v>0.0833</v>
       </c>
       <c r="X49">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="Y49">
-        <v>90.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="Z49">
         <v>73.40000000000001</v>
@@ -16551,7 +16551,7 @@
         <v>95.8</v>
       </c>
       <c r="AG49">
-        <v>92.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AH49">
         <v>44.3</v>
@@ -16632,13 +16632,13 @@
         <v>0.1</v>
       </c>
       <c r="BH49">
-        <v>1.1359</v>
+        <v>1.136</v>
       </c>
       <c r="BI49" t="s">
         <v>371</v>
       </c>
       <c r="BJ49">
-        <v>2541</v>
+        <v>2538</v>
       </c>
       <c r="BK49" t="s">
         <v>137</v>
@@ -16674,10 +16674,10 @@
         <v>60.6</v>
       </c>
       <c r="BV49">
-        <v>56.4</v>
+        <v>56.3</v>
       </c>
       <c r="BW49">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="BX49">
         <v>0.1</v>
@@ -16686,7 +16686,7 @@
         <v>196</v>
       </c>
       <c r="BZ49">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CA49" t="s">
         <v>196</v>
@@ -16695,7 +16695,7 @@
         <v>92</v>
       </c>
       <c r="CC49">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="CD49">
         <v>6</v>
@@ -16724,25 +16724,25 @@
         <v>118</v>
       </c>
       <c r="G50" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I50" t="s">
         <v>352</v>
       </c>
       <c r="J50">
-        <v>510.2</v>
+        <v>510.8</v>
       </c>
       <c r="K50">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L50">
         <v>5</v>
       </c>
       <c r="M50">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="N50">
         <v>0.45</v>
@@ -16775,13 +16775,13 @@
         <v>0.1167</v>
       </c>
       <c r="X50">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="Y50">
-        <v>91.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="Z50">
-        <v>70.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AA50">
         <v>0.9</v>
@@ -16799,13 +16799,13 @@
         <v>143</v>
       </c>
       <c r="AF50">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AG50">
-        <v>92.2</v>
+        <v>93.2</v>
       </c>
       <c r="AH50">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="AI50">
         <v>55.3</v>
@@ -16883,13 +16883,13 @@
         <v>0.08</v>
       </c>
       <c r="BH50">
-        <v>1.1564</v>
+        <v>1.156</v>
       </c>
       <c r="BI50" t="s">
         <v>371</v>
       </c>
       <c r="BJ50">
-        <v>1736</v>
+        <v>1748</v>
       </c>
       <c r="BK50" t="s">
         <v>137</v>
@@ -16898,10 +16898,10 @@
         <v>140</v>
       </c>
       <c r="BM50">
-        <v>72.7</v>
+        <v>72.8</v>
       </c>
       <c r="BN50">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="BO50">
         <v>16.2</v>
@@ -16922,13 +16922,13 @@
         <v>71.40000000000001</v>
       </c>
       <c r="BU50">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="BV50">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="BW50">
-        <v>59.6</v>
+        <v>59.2</v>
       </c>
       <c r="BX50">
         <v>0.9</v>
@@ -16937,7 +16937,7 @@
         <v>196</v>
       </c>
       <c r="BZ50">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="CA50" t="s">
         <v>196</v>
@@ -16946,7 +16946,7 @@
         <v>83</v>
       </c>
       <c r="CC50">
-        <v>83.5</v>
+        <v>83.8</v>
       </c>
       <c r="CD50">
         <v>10</v>
@@ -16975,25 +16975,25 @@
         <v>314</v>
       </c>
       <c r="G51" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I51" t="s">
         <v>352</v>
       </c>
       <c r="J51">
-        <v>510.2</v>
+        <v>510.8</v>
       </c>
       <c r="K51">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L51">
         <v>5</v>
       </c>
       <c r="M51">
-        <v>2.27</v>
+        <v>2.77</v>
       </c>
       <c r="N51">
         <v>0.71</v>
@@ -17026,13 +17026,13 @@
         <v>0.1167</v>
       </c>
       <c r="X51">
-        <v>11.2</v>
+        <v>13.2</v>
       </c>
       <c r="Y51">
-        <v>93.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Z51">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="AA51">
         <v>0.9</v>
@@ -17050,13 +17050,13 @@
         <v>143</v>
       </c>
       <c r="AF51">
-        <v>83.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="AG51">
-        <v>90.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AH51">
-        <v>64.90000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="AI51">
         <v>54.8</v>
@@ -17134,13 +17134,13 @@
         <v>0.08</v>
       </c>
       <c r="BH51">
-        <v>1.1568</v>
+        <v>1.156</v>
       </c>
       <c r="BI51" t="s">
         <v>371</v>
       </c>
       <c r="BJ51">
-        <v>1727</v>
+        <v>1749</v>
       </c>
       <c r="BK51" t="s">
         <v>137</v>
@@ -17149,10 +17149,10 @@
         <v>140</v>
       </c>
       <c r="BM51">
-        <v>73.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="BN51">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="BO51">
         <v>16.8</v>
@@ -17167,19 +17167,19 @@
         <v>1.056</v>
       </c>
       <c r="BS51">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="BT51">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="BU51">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="BV51">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="BW51">
-        <v>60.2</v>
+        <v>59.6</v>
       </c>
       <c r="BX51">
         <v>0.9</v>
@@ -17188,7 +17188,7 @@
         <v>196</v>
       </c>
       <c r="BZ51">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="CA51" t="s">
         <v>196</v>
@@ -17197,7 +17197,7 @@
         <v>83</v>
       </c>
       <c r="CC51">
-        <v>82.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="CD51">
         <v>10</v>
@@ -17226,25 +17226,25 @@
         <v>315</v>
       </c>
       <c r="G52" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H52" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I52" t="s">
         <v>352</v>
       </c>
       <c r="J52">
-        <v>510.2</v>
+        <v>510.8</v>
       </c>
       <c r="K52">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="L52">
         <v>5</v>
       </c>
       <c r="M52">
-        <v>1.82</v>
+        <v>2.43</v>
       </c>
       <c r="N52">
         <v>0.8100000000000001</v>
@@ -17277,10 +17277,10 @@
         <v>0.1167</v>
       </c>
       <c r="X52">
-        <v>9.699999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="Y52">
-        <v>91.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="Z52">
         <v>71.09999999999999</v>
@@ -17301,13 +17301,13 @@
         <v>143</v>
       </c>
       <c r="AF52">
-        <v>83.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="AG52">
-        <v>89.3</v>
+        <v>91</v>
       </c>
       <c r="AH52">
-        <v>64.8</v>
+        <v>65.2</v>
       </c>
       <c r="AI52">
         <v>53.9</v>
@@ -17385,13 +17385,13 @@
         <v>0.08</v>
       </c>
       <c r="BH52">
-        <v>1.1561</v>
+        <v>1.155</v>
       </c>
       <c r="BI52" t="s">
         <v>371</v>
       </c>
       <c r="BJ52">
-        <v>1750</v>
+        <v>1778</v>
       </c>
       <c r="BK52" t="s">
         <v>137</v>
@@ -17400,10 +17400,10 @@
         <v>140</v>
       </c>
       <c r="BM52">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="BN52">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="BO52">
         <v>16.4</v>
@@ -17418,19 +17418,19 @@
         <v>1.055</v>
       </c>
       <c r="BS52">
-        <v>72.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="BT52">
-        <v>71.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="BU52">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="BV52">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="BW52">
-        <v>60.1</v>
+        <v>59.4</v>
       </c>
       <c r="BX52">
         <v>0.9</v>
@@ -17439,7 +17439,7 @@
         <v>196</v>
       </c>
       <c r="BZ52">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="CA52" t="s">
         <v>196</v>
@@ -17448,7 +17448,7 @@
         <v>84</v>
       </c>
       <c r="CC52">
-        <v>82.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="CD52">
         <v>10</v>
@@ -17477,25 +17477,25 @@
         <v>316</v>
       </c>
       <c r="G53" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H53" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I53" t="s">
         <v>352</v>
       </c>
       <c r="J53">
-        <v>510.2</v>
+        <v>510.8</v>
       </c>
       <c r="K53">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="L53">
         <v>5</v>
       </c>
       <c r="M53">
-        <v>1.81</v>
+        <v>2.52</v>
       </c>
       <c r="N53">
         <v>0.98</v>
@@ -17528,13 +17528,13 @@
         <v>0.1167</v>
       </c>
       <c r="X53">
-        <v>10.2</v>
+        <v>13</v>
       </c>
       <c r="Y53">
-        <v>91</v>
+        <v>90.7</v>
       </c>
       <c r="Z53">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="AA53">
         <v>0.9</v>
@@ -17552,13 +17552,13 @@
         <v>143</v>
       </c>
       <c r="AF53">
-        <v>83.3</v>
+        <v>83.8</v>
       </c>
       <c r="AG53">
-        <v>86.3</v>
+        <v>88.5</v>
       </c>
       <c r="AH53">
-        <v>64</v>
+        <v>64.5</v>
       </c>
       <c r="AI53">
         <v>53.6</v>
@@ -17636,13 +17636,13 @@
         <v>0.08</v>
       </c>
       <c r="BH53">
-        <v>1.1566</v>
+        <v>1.1553</v>
       </c>
       <c r="BI53" t="s">
         <v>371</v>
       </c>
       <c r="BJ53">
-        <v>1743</v>
+        <v>1777</v>
       </c>
       <c r="BK53" t="s">
         <v>137</v>
@@ -17651,10 +17651,10 @@
         <v>140</v>
       </c>
       <c r="BM53">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="BN53">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="BO53">
         <v>16.3</v>
@@ -17669,19 +17669,19 @@
         <v>1.055</v>
       </c>
       <c r="BS53">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="BT53">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="BU53">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="BV53">
-        <v>55.7</v>
+        <v>55.9</v>
       </c>
       <c r="BW53">
-        <v>60.4</v>
+        <v>59.8</v>
       </c>
       <c r="BX53">
         <v>0.9</v>
@@ -17690,7 +17690,7 @@
         <v>196</v>
       </c>
       <c r="BZ53">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="CA53" t="s">
         <v>196</v>
@@ -17699,7 +17699,7 @@
         <v>84</v>
       </c>
       <c r="CC53">
-        <v>81.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="CD53">
         <v>10</v>
@@ -17728,16 +17728,16 @@
         <v>119</v>
       </c>
       <c r="G54" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I54" t="s">
         <v>353</v>
       </c>
       <c r="J54">
-        <v>547</v>
+        <v>547.7</v>
       </c>
       <c r="K54">
         <v>4.6</v>
@@ -17746,7 +17746,7 @@
         <v>5</v>
       </c>
       <c r="M54">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="N54">
         <v>0.6899999999999999</v>
@@ -17779,10 +17779,10 @@
         <v>0.1667</v>
       </c>
       <c r="X54">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Y54">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="Z54">
         <v>48.2</v>
@@ -17803,13 +17803,13 @@
         <v>143</v>
       </c>
       <c r="AF54">
-        <v>69.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="AG54">
-        <v>72.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AH54">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="AI54">
         <v>63.2</v>
@@ -17887,13 +17887,13 @@
         <v>0.18</v>
       </c>
       <c r="BH54">
-        <v>1.1928</v>
+        <v>1.193</v>
       </c>
       <c r="BI54" t="s">
         <v>370</v>
       </c>
       <c r="BJ54">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="BK54" t="s">
         <v>137</v>
@@ -17905,7 +17905,7 @@
         <v>48.1</v>
       </c>
       <c r="BN54">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BO54">
         <v>-3.3</v>
@@ -17926,10 +17926,10 @@
         <v>46.2</v>
       </c>
       <c r="BU54">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="BV54">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="BW54">
         <v>74.5</v>
@@ -17941,7 +17941,7 @@
         <v>196</v>
       </c>
       <c r="BZ54">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="CA54" t="s">
         <v>196</v>
@@ -17950,7 +17950,7 @@
         <v>71</v>
       </c>
       <c r="CC54">
-        <v>70.3</v>
+        <v>70.2</v>
       </c>
       <c r="CD54">
         <v>8</v>
@@ -17979,16 +17979,16 @@
         <v>317</v>
       </c>
       <c r="G55" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H55" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I55" t="s">
         <v>353</v>
       </c>
       <c r="J55">
-        <v>547</v>
+        <v>547.7</v>
       </c>
       <c r="K55">
         <v>5.6</v>
@@ -17997,7 +17997,7 @@
         <v>5</v>
       </c>
       <c r="M55">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="N55">
         <v>0.77</v>
@@ -18030,10 +18030,10 @@
         <v>0.1667</v>
       </c>
       <c r="X55">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y55">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="Z55">
         <v>47.8</v>
@@ -18057,10 +18057,10 @@
         <v>70.90000000000001</v>
       </c>
       <c r="AG55">
-        <v>73.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AH55">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="AI55">
         <v>59.1</v>
@@ -18138,13 +18138,13 @@
         <v>0.18</v>
       </c>
       <c r="BH55">
-        <v>1.1894</v>
+        <v>1.1896</v>
       </c>
       <c r="BI55" t="s">
         <v>370</v>
       </c>
       <c r="BJ55">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="BK55" t="s">
         <v>137</v>
@@ -18177,7 +18177,7 @@
         <v>45.6</v>
       </c>
       <c r="BU55">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
       <c r="BV55">
         <v>49.3</v>
@@ -18192,7 +18192,7 @@
         <v>196</v>
       </c>
       <c r="BZ55">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="CA55" t="s">
         <v>196</v>
@@ -18201,7 +18201,7 @@
         <v>72</v>
       </c>
       <c r="CC55">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="CD55">
         <v>9</v>
@@ -18230,16 +18230,16 @@
         <v>318</v>
       </c>
       <c r="G56" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I56" t="s">
         <v>353</v>
       </c>
       <c r="J56">
-        <v>547</v>
+        <v>547.7</v>
       </c>
       <c r="K56">
         <v>6.6</v>
@@ -18248,7 +18248,7 @@
         <v>5</v>
       </c>
       <c r="M56">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="N56">
         <v>0.76</v>
@@ -18281,10 +18281,10 @@
         <v>0.1667</v>
       </c>
       <c r="X56">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y56">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Z56">
         <v>47.6</v>
@@ -18305,13 +18305,13 @@
         <v>143</v>
       </c>
       <c r="AF56">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="AG56">
-        <v>74.8</v>
+        <v>74.2</v>
       </c>
       <c r="AH56">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="AI56">
         <v>56.4</v>
@@ -18389,13 +18389,13 @@
         <v>0.18</v>
       </c>
       <c r="BH56">
-        <v>1.1854</v>
+        <v>1.1857</v>
       </c>
       <c r="BI56" t="s">
         <v>370</v>
       </c>
       <c r="BJ56">
-        <v>937</v>
+        <v>928</v>
       </c>
       <c r="BK56" t="s">
         <v>137</v>
@@ -18404,10 +18404,10 @@
         <v>142</v>
       </c>
       <c r="BM56">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="BN56">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BO56">
         <v>-4.7</v>
@@ -18425,7 +18425,7 @@
         <v>50</v>
       </c>
       <c r="BT56">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="BU56">
         <v>53.7</v>
@@ -18434,7 +18434,7 @@
         <v>49.5</v>
       </c>
       <c r="BW56">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="BX56">
         <v>0</v>
@@ -18443,7 +18443,7 @@
         <v>196</v>
       </c>
       <c r="BZ56">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="CA56" t="s">
         <v>196</v>
@@ -18452,7 +18452,7 @@
         <v>74</v>
       </c>
       <c r="CC56">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="CD56">
         <v>9</v>
@@ -18481,16 +18481,16 @@
         <v>319</v>
       </c>
       <c r="G57" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H57" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I57" t="s">
         <v>353</v>
       </c>
       <c r="J57">
-        <v>547</v>
+        <v>547.7</v>
       </c>
       <c r="K57">
         <v>7.6</v>
@@ -18499,7 +18499,7 @@
         <v>5</v>
       </c>
       <c r="M57">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="N57">
         <v>0.85</v>
@@ -18532,10 +18532,10 @@
         <v>0.1667</v>
       </c>
       <c r="X57">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="Y57">
-        <v>94.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Z57">
         <v>47</v>
@@ -18556,13 +18556,13 @@
         <v>143</v>
       </c>
       <c r="AF57">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="AG57">
-        <v>74.3</v>
+        <v>73.7</v>
       </c>
       <c r="AH57">
-        <v>56.3</v>
+        <v>56.1</v>
       </c>
       <c r="AI57">
         <v>54.1</v>
@@ -18640,13 +18640,13 @@
         <v>0.18</v>
       </c>
       <c r="BH57">
-        <v>1.1833</v>
+        <v>1.1838</v>
       </c>
       <c r="BI57" t="s">
         <v>370</v>
       </c>
       <c r="BJ57">
-        <v>999</v>
+        <v>987</v>
       </c>
       <c r="BK57" t="s">
         <v>137</v>
@@ -18655,10 +18655,10 @@
         <v>142</v>
       </c>
       <c r="BM57">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="BN57">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BO57">
         <v>-5.5</v>
@@ -18682,10 +18682,10 @@
         <v>53.7</v>
       </c>
       <c r="BV57">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="BW57">
-        <v>71.5</v>
+        <v>71.7</v>
       </c>
       <c r="BX57">
         <v>0</v>
@@ -18694,7 +18694,7 @@
         <v>196</v>
       </c>
       <c r="BZ57">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="CA57" t="s">
         <v>196</v>
@@ -18703,7 +18703,7 @@
         <v>75</v>
       </c>
       <c r="CC57">
-        <v>73.5</v>
+        <v>73.2</v>
       </c>
       <c r="CD57">
         <v>10</v>
@@ -18732,16 +18732,16 @@
         <v>120</v>
       </c>
       <c r="G58" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H58" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I58" t="s">
         <v>354</v>
       </c>
       <c r="J58">
-        <v>281.6</v>
+        <v>282.2</v>
       </c>
       <c r="K58">
         <v>4.6</v>
@@ -18750,7 +18750,7 @@
         <v>5</v>
       </c>
       <c r="M58">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="N58">
         <v>0.67</v>
@@ -18783,13 +18783,13 @@
         <v>0.1667</v>
       </c>
       <c r="X58">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
       <c r="Y58">
-        <v>89.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z58">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="AA58">
         <v>0.74</v>
@@ -18810,10 +18810,10 @@
         <v>98.5</v>
       </c>
       <c r="AG58">
-        <v>107.8</v>
+        <v>108.4</v>
       </c>
       <c r="AH58">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="AI58">
         <v>34.3</v>
@@ -18945,7 +18945,7 @@
         <v>198</v>
       </c>
       <c r="BZ58">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="CA58" t="s">
         <v>196</v>
@@ -18954,7 +18954,7 @@
         <v>98</v>
       </c>
       <c r="CC58">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="CD58">
         <v>5</v>
@@ -18983,16 +18983,16 @@
         <v>320</v>
       </c>
       <c r="G59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H59" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I59" t="s">
         <v>354</v>
       </c>
       <c r="J59">
-        <v>281.6</v>
+        <v>282.2</v>
       </c>
       <c r="K59">
         <v>5.6</v>
@@ -19001,7 +19001,7 @@
         <v>5</v>
       </c>
       <c r="M59">
-        <v>3.38</v>
+        <v>2.57</v>
       </c>
       <c r="N59">
         <v>1.14</v>
@@ -19034,13 +19034,13 @@
         <v>0.1667</v>
       </c>
       <c r="X59">
-        <v>17.8</v>
+        <v>14.6</v>
       </c>
       <c r="Y59">
-        <v>88.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Z59">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="AA59">
         <v>0.74</v>
@@ -19058,19 +19058,19 @@
         <v>144</v>
       </c>
       <c r="AF59">
-        <v>99.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AG59">
-        <v>109.5</v>
+        <v>102.9</v>
       </c>
       <c r="AH59">
-        <v>64.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="AI59">
         <v>32.4</v>
       </c>
       <c r="AJ59">
-        <v>971.9</v>
+        <v>971.8</v>
       </c>
       <c r="AK59">
         <v>1008.9</v>
@@ -19196,7 +19196,7 @@
         <v>198</v>
       </c>
       <c r="BZ59">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="CA59" t="s">
         <v>196</v>
@@ -19205,7 +19205,7 @@
         <v>98</v>
       </c>
       <c r="CC59">
-        <v>100.4</v>
+        <v>99.2</v>
       </c>
       <c r="CD59">
         <v>5</v>
@@ -19234,16 +19234,16 @@
         <v>321</v>
       </c>
       <c r="G60" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H60" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I60" t="s">
         <v>354</v>
       </c>
       <c r="J60">
-        <v>281.6</v>
+        <v>282.2</v>
       </c>
       <c r="K60">
         <v>6.6</v>
@@ -19252,7 +19252,7 @@
         <v>5</v>
       </c>
       <c r="M60">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="N60">
         <v>1.77</v>
@@ -19285,13 +19285,13 @@
         <v>0.1667</v>
       </c>
       <c r="X60">
-        <v>19.9</v>
+        <v>16.2</v>
       </c>
       <c r="Y60">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Z60">
-        <v>53.3</v>
+        <v>53.5</v>
       </c>
       <c r="AA60">
         <v>0.74</v>
@@ -19309,19 +19309,19 @@
         <v>368</v>
       </c>
       <c r="AF60">
-        <v>100.8</v>
+        <v>100.1</v>
       </c>
       <c r="AG60">
-        <v>108.9</v>
+        <v>103</v>
       </c>
       <c r="AH60">
-        <v>63.1</v>
+        <v>62.4</v>
       </c>
       <c r="AI60">
         <v>29.9</v>
       </c>
       <c r="AJ60">
-        <v>971.4</v>
+        <v>971.3</v>
       </c>
       <c r="AK60">
         <v>1008.2</v>
@@ -19447,7 +19447,7 @@
         <v>198</v>
       </c>
       <c r="BZ60">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="CA60" t="s">
         <v>196</v>
@@ -19456,7 +19456,7 @@
         <v>100</v>
       </c>
       <c r="CC60">
-        <v>101.4</v>
+        <v>100.2</v>
       </c>
       <c r="CD60">
         <v>5</v>
@@ -19485,16 +19485,16 @@
         <v>322</v>
       </c>
       <c r="G61" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H61" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I61" t="s">
         <v>354</v>
       </c>
       <c r="J61">
-        <v>281.6</v>
+        <v>282.2</v>
       </c>
       <c r="K61">
         <v>7.6</v>
@@ -19503,7 +19503,7 @@
         <v>5</v>
       </c>
       <c r="M61">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="N61">
         <v>3.19</v>
@@ -19536,13 +19536,13 @@
         <v>0.1667</v>
       </c>
       <c r="X61">
-        <v>23.2</v>
+        <v>20.5</v>
       </c>
       <c r="Y61">
-        <v>85.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Z61">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="AA61">
         <v>0.74</v>
@@ -19560,13 +19560,13 @@
         <v>368</v>
       </c>
       <c r="AF61">
-        <v>100.9</v>
+        <v>100.5</v>
       </c>
       <c r="AG61">
-        <v>105.8</v>
+        <v>102.5</v>
       </c>
       <c r="AH61">
-        <v>62.7</v>
+        <v>62.2</v>
       </c>
       <c r="AI61">
         <v>29.3</v>
@@ -19698,7 +19698,7 @@
         <v>198</v>
       </c>
       <c r="BZ61">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="CA61" t="s">
         <v>196</v>
@@ -19707,7 +19707,7 @@
         <v>100</v>
       </c>
       <c r="CC61">
-        <v>101.6</v>
+        <v>100.8</v>
       </c>
       <c r="CD61">
         <v>5</v>
@@ -19745,7 +19745,7 @@
         <v>341</v>
       </c>
       <c r="J62">
-        <v>424.3</v>
+        <v>425</v>
       </c>
       <c r="K62">
         <v>7.8</v>
@@ -19754,7 +19754,7 @@
         <v>5</v>
       </c>
       <c r="M62">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="N62">
         <v>1.93</v>
@@ -19787,13 +19787,13 @@
         <v>0.3333</v>
       </c>
       <c r="X62">
-        <v>11.8</v>
+        <v>12.9</v>
       </c>
       <c r="Y62">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="Z62">
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
       <c r="AA62">
         <v>0.92</v>
@@ -19811,13 +19811,13 @@
         <v>143</v>
       </c>
       <c r="AF62">
-        <v>78.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AG62">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="AH62">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="AI62">
         <v>40.9</v>
@@ -19895,13 +19895,13 @@
         <v>0.12</v>
       </c>
       <c r="BH62">
-        <v>1.1705</v>
+        <v>1.1698</v>
       </c>
       <c r="BI62" t="s">
         <v>370</v>
       </c>
       <c r="BJ62">
-        <v>1416</v>
+        <v>1434</v>
       </c>
       <c r="BK62" t="s">
         <v>137</v>
@@ -19928,7 +19928,7 @@
         <v>1.032</v>
       </c>
       <c r="BS62">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="BT62">
         <v>60.5</v>
@@ -19937,10 +19937,10 @@
         <v>58.2</v>
       </c>
       <c r="BV62">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="BW62">
-        <v>66.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="BX62">
         <v>0</v>
@@ -19949,7 +19949,7 @@
         <v>196</v>
       </c>
       <c r="BZ62">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="CA62" t="s">
         <v>196</v>
@@ -19958,7 +19958,7 @@
         <v>78</v>
       </c>
       <c r="CC62">
-        <v>77.3</v>
+        <v>77.8</v>
       </c>
       <c r="CD62">
         <v>7</v>
@@ -19996,7 +19996,7 @@
         <v>341</v>
       </c>
       <c r="J63">
-        <v>424.3</v>
+        <v>425</v>
       </c>
       <c r="K63">
         <v>8.800000000000001</v>
@@ -20005,7 +20005,7 @@
         <v>5</v>
       </c>
       <c r="M63">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="N63">
         <v>1.03</v>
@@ -20038,13 +20038,13 @@
         <v>0.3333</v>
       </c>
       <c r="X63">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="Y63">
-        <v>93.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="Z63">
-        <v>60.8</v>
+        <v>61</v>
       </c>
       <c r="AA63">
         <v>0.92</v>
@@ -20062,13 +20062,13 @@
         <v>143</v>
       </c>
       <c r="AF63">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="AG63">
-        <v>71</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AH63">
-        <v>51.7</v>
+        <v>52.3</v>
       </c>
       <c r="AI63">
         <v>45.1</v>
@@ -20146,13 +20146,13 @@
         <v>0.12</v>
       </c>
       <c r="BH63">
-        <v>1.1769</v>
+        <v>1.1757</v>
       </c>
       <c r="BI63" t="s">
         <v>370</v>
       </c>
       <c r="BJ63">
-        <v>1219</v>
+        <v>1253</v>
       </c>
       <c r="BK63" t="s">
         <v>137</v>
@@ -20161,10 +20161,10 @@
         <v>140</v>
       </c>
       <c r="BM63">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
       <c r="BN63">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO63">
         <v>6.1</v>
@@ -20179,19 +20179,19 @@
         <v>1.028</v>
       </c>
       <c r="BS63">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="BT63">
-        <v>59.4</v>
+        <v>59.6</v>
       </c>
       <c r="BU63">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="BV63">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="BW63">
-        <v>69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="BX63">
         <v>0</v>
@@ -20200,7 +20200,7 @@
         <v>196</v>
       </c>
       <c r="BZ63">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="CA63" t="s">
         <v>196</v>
@@ -20209,7 +20209,7 @@
         <v>76</v>
       </c>
       <c r="CC63">
-        <v>74.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="CD63">
         <v>6</v>
@@ -20247,7 +20247,7 @@
         <v>341</v>
       </c>
       <c r="J64">
-        <v>424.3</v>
+        <v>425</v>
       </c>
       <c r="K64">
         <v>9.800000000000001</v>
@@ -20256,7 +20256,7 @@
         <v>5</v>
       </c>
       <c r="M64">
-        <v>1.5</v>
+        <v>0.96</v>
       </c>
       <c r="N64">
         <v>0.73</v>
@@ -20289,13 +20289,13 @@
         <v>0.3333</v>
       </c>
       <c r="X64">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="Y64">
-        <v>90.2</v>
+        <v>92.3</v>
       </c>
       <c r="Z64">
-        <v>59.4</v>
+        <v>59.7</v>
       </c>
       <c r="AA64">
         <v>0.92</v>
@@ -20313,13 +20313,13 @@
         <v>143</v>
       </c>
       <c r="AF64">
-        <v>73.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AG64">
-        <v>67.8</v>
+        <v>70.2</v>
       </c>
       <c r="AH64">
-        <v>52.5</v>
+        <v>53.2</v>
       </c>
       <c r="AI64">
         <v>49.3</v>
@@ -20397,13 +20397,13 @@
         <v>0.12</v>
       </c>
       <c r="BH64">
-        <v>1.1823</v>
+        <v>1.1809</v>
       </c>
       <c r="BI64" t="s">
         <v>370</v>
       </c>
       <c r="BJ64">
-        <v>1054</v>
+        <v>1093</v>
       </c>
       <c r="BK64" t="s">
         <v>137</v>
@@ -20412,10 +20412,10 @@
         <v>140</v>
       </c>
       <c r="BM64">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="BN64">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO64">
         <v>5.4</v>
@@ -20430,19 +20430,19 @@
         <v>1.025</v>
       </c>
       <c r="BS64">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="BT64">
-        <v>58.3</v>
+        <v>58.5</v>
       </c>
       <c r="BU64">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="BV64">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="BW64">
-        <v>71.3</v>
+        <v>70.7</v>
       </c>
       <c r="BX64">
         <v>0</v>
@@ -20451,7 +20451,7 @@
         <v>196</v>
       </c>
       <c r="BZ64">
-        <v>11.1</v>
+        <v>9</v>
       </c>
       <c r="CA64" t="s">
         <v>196</v>
@@ -20460,7 +20460,7 @@
         <v>75</v>
       </c>
       <c r="CC64">
-        <v>71.3</v>
+        <v>72.3</v>
       </c>
       <c r="CD64">
         <v>6</v>
@@ -20498,7 +20498,7 @@
         <v>341</v>
       </c>
       <c r="J65">
-        <v>424.3</v>
+        <v>425</v>
       </c>
       <c r="K65">
         <v>10.8</v>
@@ -20507,7 +20507,7 @@
         <v>5</v>
       </c>
       <c r="M65">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="N65">
         <v>0.78</v>
@@ -20540,13 +20540,13 @@
         <v>0.3333</v>
       </c>
       <c r="X65">
-        <v>10.1</v>
+        <v>8</v>
       </c>
       <c r="Y65">
-        <v>88.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z65">
-        <v>57.9</v>
+        <v>58.2</v>
       </c>
       <c r="AA65">
         <v>0.92</v>
@@ -20564,13 +20564,13 @@
         <v>143</v>
       </c>
       <c r="AF65">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AG65">
-        <v>66.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AH65">
-        <v>53.5</v>
+        <v>54.1</v>
       </c>
       <c r="AI65">
         <v>54.5</v>
@@ -20648,13 +20648,13 @@
         <v>0.12</v>
       </c>
       <c r="BH65">
-        <v>1.1873</v>
+        <v>1.1861</v>
       </c>
       <c r="BI65" t="s">
         <v>370</v>
       </c>
       <c r="BJ65">
-        <v>902</v>
+        <v>933</v>
       </c>
       <c r="BK65" t="s">
         <v>137</v>
@@ -20663,10 +20663,10 @@
         <v>140</v>
       </c>
       <c r="BM65">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="BN65">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BO65">
         <v>4.5</v>
@@ -20678,22 +20678,22 @@
         <v>0</v>
       </c>
       <c r="BR65">
-        <v>1.021</v>
+        <v>1.022</v>
       </c>
       <c r="BS65">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="BT65">
-        <v>56.6</v>
+        <v>56.8</v>
       </c>
       <c r="BU65">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="BV65">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="BW65">
-        <v>73.5</v>
+        <v>73</v>
       </c>
       <c r="BX65">
         <v>0</v>
@@ -20702,7 +20702,7 @@
         <v>196</v>
       </c>
       <c r="BZ65">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="CA65" t="s">
         <v>196</v>
@@ -20711,7 +20711,7 @@
         <v>73</v>
       </c>
       <c r="CC65">
-        <v>69.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="CD65">
         <v>7</v>
@@ -20819,13 +20819,13 @@
         <v>132</v>
       </c>
       <c r="E2">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F2" t="s">
         <v>170</v>
       </c>
       <c r="G2">
-        <v>93.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -20834,7 +20834,7 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K2">
         <v>-2</v>
@@ -20843,10 +20843,10 @@
         <v>189</v>
       </c>
       <c r="M2">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N2">
-        <v>8603</v>
+        <v>8614</v>
       </c>
       <c r="O2" t="s">
         <v>137</v>
@@ -20878,7 +20878,7 @@
         <v>170</v>
       </c>
       <c r="G3">
-        <v>92.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H3">
         <v>9</v>
@@ -20896,10 +20896,10 @@
         <v>189</v>
       </c>
       <c r="M3">
-        <v>83.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="N3">
-        <v>1737</v>
+        <v>1757</v>
       </c>
       <c r="O3" t="s">
         <v>137</v>
@@ -20931,7 +20931,7 @@
         <v>170</v>
       </c>
       <c r="G4">
-        <v>88.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="H4">
         <v>9</v>
@@ -20949,10 +20949,10 @@
         <v>189</v>
       </c>
       <c r="M4">
-        <v>92.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N4">
-        <v>2289</v>
+        <v>2280</v>
       </c>
       <c r="O4" t="s">
         <v>137</v>
@@ -20984,10 +20984,10 @@
         <v>170</v>
       </c>
       <c r="G5">
-        <v>88.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -21002,10 +21002,10 @@
         <v>189</v>
       </c>
       <c r="M5">
-        <v>91.5</v>
+        <v>91.8</v>
       </c>
       <c r="N5">
-        <v>3233</v>
+        <v>3256</v>
       </c>
       <c r="O5" t="s">
         <v>137</v>
@@ -21037,7 +21037,7 @@
         <v>170</v>
       </c>
       <c r="G6">
-        <v>92.3</v>
+        <v>91.5</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -21055,10 +21055,10 @@
         <v>189</v>
       </c>
       <c r="M6">
-        <v>80.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="N6">
-        <v>1583</v>
+        <v>1611</v>
       </c>
       <c r="O6" t="s">
         <v>137</v>
@@ -21090,7 +21090,7 @@
         <v>169</v>
       </c>
       <c r="G7">
-        <v>88.5</v>
+        <v>88.8</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -21111,7 +21111,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="N7">
-        <v>3241</v>
+        <v>3238</v>
       </c>
       <c r="O7" t="s">
         <v>137</v>
@@ -21137,22 +21137,22 @@
         <v>123</v>
       </c>
       <c r="E8">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="F8" t="s">
         <v>169</v>
       </c>
       <c r="G8">
-        <v>92.3</v>
+        <v>93.2</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K8">
         <v>2</v>
@@ -21161,10 +21161,10 @@
         <v>188</v>
       </c>
       <c r="M8">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="N8">
-        <v>1233</v>
+        <v>1261</v>
       </c>
       <c r="O8" t="s">
         <v>137</v>
@@ -21231,16 +21231,16 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E10">
         <v>51.5</v>
@@ -21249,7 +21249,7 @@
         <v>169</v>
       </c>
       <c r="G10">
-        <v>95.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -21261,16 +21261,16 @@
         <v>0.4</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="L10" t="s">
         <v>188</v>
       </c>
       <c r="M10">
-        <v>72.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="N10">
-        <v>1172</v>
+        <v>1639</v>
       </c>
       <c r="O10" t="s">
         <v>137</v>
@@ -21279,30 +21279,30 @@
         <v>196</v>
       </c>
       <c r="Q10">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E11">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F11" t="s">
         <v>169</v>
       </c>
       <c r="G11">
-        <v>86.7</v>
+        <v>95.8</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -21314,16 +21314,16 @@
         <v>0.4</v>
       </c>
       <c r="K11">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L11" t="s">
         <v>188</v>
       </c>
       <c r="M11">
-        <v>81.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="N11">
-        <v>1634</v>
+        <v>1130</v>
       </c>
       <c r="O11" t="s">
         <v>137</v>
@@ -21332,7 +21332,7 @@
         <v>196</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -21355,7 +21355,7 @@
         <v>169</v>
       </c>
       <c r="G12">
-        <v>94.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -21376,7 +21376,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="N12">
-        <v>1944</v>
+        <v>1939</v>
       </c>
       <c r="O12" t="s">
         <v>137</v>
@@ -21408,7 +21408,7 @@
         <v>169</v>
       </c>
       <c r="G13">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -21426,10 +21426,10 @@
         <v>188</v>
       </c>
       <c r="M13">
-        <v>70.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="N13">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="O13" t="s">
         <v>137</v>
@@ -21479,7 +21479,7 @@
         <v>188</v>
       </c>
       <c r="M14">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="N14">
         <v>858</v>
@@ -21514,7 +21514,7 @@
         <v>169</v>
       </c>
       <c r="G15">
-        <v>88.7</v>
+        <v>90.2</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -21532,7 +21532,7 @@
         <v>188</v>
       </c>
       <c r="M15">
-        <v>99.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N15">
         <v>858</v>
@@ -21567,7 +21567,7 @@
         <v>171</v>
       </c>
       <c r="G16">
-        <v>90.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="H16">
         <v>-2</v>
@@ -21585,10 +21585,10 @@
         <v>190</v>
       </c>
       <c r="M16">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="N16">
-        <v>1639</v>
+        <v>1627</v>
       </c>
       <c r="O16" t="s">
         <v>137</v>
@@ -21620,7 +21620,7 @@
         <v>171</v>
       </c>
       <c r="G17">
-        <v>92</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H17">
         <v>-4</v>
@@ -21638,10 +21638,10 @@
         <v>190</v>
       </c>
       <c r="M17">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="N17">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="O17" t="s">
         <v>137</v>
